--- a/data/UK-BDI-2025-habitat-connectivity.xlsx
+++ b/data/UK-BDI-2025-habitat-connectivity.xlsx
@@ -1,11 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0E4C1328-A2DE-4300-A8DA-2506228FE021}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FDDC8F90-5A1D-4CDA-8DCB-4944AB190750}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="10" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Cover_sheet" sheetId="4" r:id="rId1"/>
@@ -819,7 +819,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="x14ac x16r2 xr xr9">
-  <fonts count="14" x14ac:knownFonts="1">
+  <fonts count="15" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -906,6 +906,13 @@
       <name val="Arial"/>
       <family val="2"/>
     </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -928,7 +935,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="31">
+  <cellXfs count="32">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -952,9 +959,6 @@
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -1018,6 +1022,12 @@
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="14" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -2579,9 +2589,9 @@
   <dimension ref="A1:A15"/>
   <sheetFormatPr defaultColWidth="10.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="116.85546875" style="18" customWidth="1"/>
-    <col min="2" max="2" width="9.7109375" style="18" customWidth="1"/>
-    <col min="3" max="16384" width="10.85546875" style="18"/>
+    <col min="1" max="1" width="116.85546875" style="17" customWidth="1"/>
+    <col min="2" max="2" width="9.7109375" style="17" customWidth="1"/>
+    <col min="3" max="16384" width="10.85546875" style="17"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
@@ -2590,72 +2600,72 @@
       </c>
     </row>
     <row r="2" spans="1:1" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="27" t="s">
+      <c r="A2" s="26" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="3" spans="1:1" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="28" t="s">
+      <c r="A3" s="27" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="4" spans="1:1" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="29" t="s">
+      <c r="A4" s="28" t="s">
         <v>255</v>
       </c>
     </row>
     <row r="5" spans="1:1" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="27" t="s">
+      <c r="A5" s="26" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="6" spans="1:1" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="28" t="s">
+      <c r="A6" s="27" t="s">
         <v>254</v>
       </c>
     </row>
     <row r="7" spans="1:1" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="27" t="s">
+      <c r="A7" s="26" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="8" spans="1:1" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="29" t="s">
+      <c r="A8" s="28" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="9" spans="1:1" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="27" t="s">
+      <c r="A9" s="26" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="10" spans="1:1" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="28" t="s">
+      <c r="A10" s="27" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="11" spans="1:1" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="27" t="s">
+      <c r="A11" s="26" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="12" spans="1:1" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="28" t="s">
+      <c r="A12" s="27" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="13" spans="1:1" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="28" t="s">
+      <c r="A13" s="27" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="14" spans="1:1" ht="15.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A14" s="30" t="s">
+      <c r="A14" s="29" t="s">
         <v>256</v>
       </c>
     </row>
     <row r="15" spans="1:1" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="28" t="s">
+      <c r="A15" s="27" t="s">
         <v>11</v>
       </c>
     </row>
@@ -2666,6 +2676,9 @@
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+  <headerFooter>
+    <oddHeader>&amp;C&amp;"Aptos"&amp;10&amp;K000000 CLASSIFICATION: CONFIDENTIAL - COMMERCIAL IN CONFIDENCE&amp;1#_x000D_</oddHeader>
+  </headerFooter>
 </worksheet>
 </file>
 
@@ -2674,105 +2687,105 @@
   <dimension ref="A1:D73"/>
   <sheetFormatPr defaultColWidth="10.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="7.7109375" style="14" customWidth="1"/>
-    <col min="2" max="2" width="41.5703125" style="14" customWidth="1"/>
-    <col min="3" max="3" width="19.85546875" style="14" customWidth="1"/>
-    <col min="4" max="16384" width="10.85546875" style="14"/>
+    <col min="1" max="1" width="7.7109375" style="13" customWidth="1"/>
+    <col min="2" max="2" width="41.5703125" style="13" customWidth="1"/>
+    <col min="3" max="3" width="19.85546875" style="13" customWidth="1"/>
+    <col min="4" max="16384" width="10.85546875" style="13"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="11" t="s">
+      <c r="A1" s="10" t="s">
         <v>246</v>
       </c>
-      <c r="B1" s="11"/>
+      <c r="B1" s="10"/>
     </row>
     <row r="2" spans="1:4" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="10" t="s">
+      <c r="A2" s="9" t="s">
         <v>247</v>
       </c>
-      <c r="B2" s="10"/>
+      <c r="B2" s="9"/>
     </row>
     <row r="3" spans="1:4" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="10" t="s">
+      <c r="A3" s="9" t="s">
         <v>43</v>
       </c>
-      <c r="B3" s="10"/>
+      <c r="B3" s="9"/>
     </row>
     <row r="4" spans="1:4" ht="48.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="16" t="s">
+      <c r="A4" s="15" t="s">
         <v>248</v>
       </c>
-      <c r="B4" s="16" t="s">
+      <c r="B4" s="15" t="s">
         <v>249</v>
       </c>
-      <c r="C4" s="16" t="s">
+      <c r="C4" s="31" t="s">
         <v>250</v>
       </c>
-      <c r="D4" s="16"/>
+      <c r="D4" s="15"/>
     </row>
     <row r="5" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="22" t="s">
+      <c r="A5" s="21" t="s">
         <v>154</v>
       </c>
-      <c r="B5" s="22" t="s">
+      <c r="B5" s="21" t="s">
         <v>251</v>
       </c>
-      <c r="C5" s="26">
+      <c r="C5" s="25">
         <v>0.13400000000000001</v>
       </c>
     </row>
     <row r="6" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="22" t="s">
+      <c r="A6" s="21" t="s">
         <v>162</v>
       </c>
-      <c r="B6" s="22" t="s">
+      <c r="B6" s="21" t="s">
         <v>251</v>
       </c>
-      <c r="C6" s="26">
+      <c r="C6" s="25">
         <v>0.1076</v>
       </c>
     </row>
     <row r="7" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="22" t="s">
+      <c r="A7" s="21" t="s">
         <v>171</v>
       </c>
-      <c r="B7" s="22" t="s">
+      <c r="B7" s="21" t="s">
         <v>251</v>
       </c>
-      <c r="C7" s="26">
+      <c r="C7" s="25">
         <v>7.4200000000000002E-2</v>
       </c>
     </row>
     <row r="8" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="22" t="s">
+      <c r="A8" s="21" t="s">
         <v>154</v>
       </c>
-      <c r="B8" s="22" t="s">
+      <c r="B8" s="21" t="s">
         <v>252</v>
       </c>
-      <c r="C8" s="26">
+      <c r="C8" s="25">
         <v>0.3463</v>
       </c>
     </row>
     <row r="9" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="22" t="s">
+      <c r="A9" s="21" t="s">
         <v>162</v>
       </c>
-      <c r="B9" s="22" t="s">
+      <c r="B9" s="21" t="s">
         <v>252</v>
       </c>
-      <c r="C9" s="26">
+      <c r="C9" s="25">
         <v>0.58260000000000001</v>
       </c>
     </row>
     <row r="10" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="22" t="s">
+      <c r="A10" s="21" t="s">
         <v>171</v>
       </c>
-      <c r="B10" s="22" t="s">
+      <c r="B10" s="21" t="s">
         <v>252</v>
       </c>
-      <c r="C10" s="26">
+      <c r="C10" s="25">
         <v>0.67559999999999998</v>
       </c>
     </row>
@@ -2842,6 +2855,9 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+  <headerFooter>
+    <oddHeader>&amp;C&amp;"Aptos"&amp;10&amp;K000000 CLASSIFICATION: CONFIDENTIAL - COMMERCIAL IN CONFIDENCE&amp;1#_x000D_</oddHeader>
+  </headerFooter>
   <tableParts count="1">
     <tablePart r:id="rId1"/>
   </tableParts>
@@ -2853,153 +2869,156 @@
   <dimension ref="A1:D15"/>
   <sheetFormatPr defaultColWidth="10.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="7.42578125" style="14" customWidth="1"/>
-    <col min="2" max="2" width="41.85546875" style="14" customWidth="1"/>
-    <col min="3" max="3" width="20.42578125" style="14" customWidth="1"/>
-    <col min="4" max="16384" width="10.85546875" style="14"/>
+    <col min="1" max="1" width="7.42578125" style="13" customWidth="1"/>
+    <col min="2" max="2" width="41.85546875" style="13" customWidth="1"/>
+    <col min="3" max="3" width="20.42578125" style="13" customWidth="1"/>
+    <col min="4" max="16384" width="10.85546875" style="13"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="11" t="s">
+      <c r="A1" s="10" t="s">
         <v>253</v>
       </c>
-      <c r="B1" s="11"/>
-      <c r="C1" s="13"/>
-      <c r="D1" s="13"/>
+      <c r="B1" s="10"/>
+      <c r="C1" s="12"/>
+      <c r="D1" s="12"/>
     </row>
     <row r="2" spans="1:4" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="10" t="s">
+      <c r="A2" s="9" t="s">
         <v>247</v>
       </c>
-      <c r="B2" s="10"/>
-      <c r="C2" s="13"/>
-      <c r="D2" s="13"/>
+      <c r="B2" s="9"/>
+      <c r="C2" s="12"/>
+      <c r="D2" s="12"/>
     </row>
     <row r="3" spans="1:4" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="10" t="s">
+      <c r="A3" s="9" t="s">
         <v>43</v>
       </c>
-      <c r="B3" s="10"/>
-      <c r="C3" s="13"/>
-      <c r="D3" s="13"/>
+      <c r="B3" s="9"/>
+      <c r="C3" s="12"/>
+      <c r="D3" s="12"/>
     </row>
     <row r="4" spans="1:4" ht="51" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="16" t="s">
+      <c r="A4" s="15" t="s">
         <v>248</v>
       </c>
-      <c r="B4" s="16" t="s">
+      <c r="B4" s="15" t="s">
         <v>249</v>
       </c>
-      <c r="C4" s="16" t="s">
+      <c r="C4" s="15" t="s">
         <v>250</v>
       </c>
-      <c r="D4" s="16"/>
+      <c r="D4" s="15"/>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A5" s="22" t="s">
+      <c r="A5" s="21" t="s">
         <v>154</v>
       </c>
-      <c r="B5" s="22" t="s">
+      <c r="B5" s="21" t="s">
         <v>251</v>
       </c>
-      <c r="C5" s="26">
+      <c r="C5" s="25">
         <v>9.2299999999999993E-2</v>
       </c>
-      <c r="D5" s="13"/>
+      <c r="D5" s="12"/>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A6" s="22" t="s">
+      <c r="A6" s="21" t="s">
         <v>162</v>
       </c>
-      <c r="B6" s="22" t="s">
+      <c r="B6" s="21" t="s">
         <v>251</v>
       </c>
-      <c r="C6" s="26">
+      <c r="C6" s="25">
         <v>6.9500000000000006E-2</v>
       </c>
-      <c r="D6" s="13"/>
+      <c r="D6" s="12"/>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A7" s="22" t="s">
+      <c r="A7" s="21" t="s">
         <v>171</v>
       </c>
-      <c r="B7" s="22" t="s">
+      <c r="B7" s="21" t="s">
         <v>251</v>
       </c>
-      <c r="C7" s="26">
+      <c r="C7" s="25">
         <v>8.6800000000000002E-2</v>
       </c>
-      <c r="D7" s="13"/>
+      <c r="D7" s="12"/>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A8" s="22" t="s">
+      <c r="A8" s="21" t="s">
         <v>154</v>
       </c>
-      <c r="B8" s="22" t="s">
+      <c r="B8" s="21" t="s">
         <v>252</v>
       </c>
-      <c r="C8" s="26">
+      <c r="C8" s="25">
         <v>0.32719999999999999</v>
       </c>
-      <c r="D8" s="13"/>
+      <c r="D8" s="12"/>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A9" s="22" t="s">
+      <c r="A9" s="21" t="s">
         <v>162</v>
       </c>
-      <c r="B9" s="22" t="s">
+      <c r="B9" s="21" t="s">
         <v>252</v>
       </c>
-      <c r="C9" s="26">
+      <c r="C9" s="25">
         <v>0.75690000000000002</v>
       </c>
-      <c r="D9" s="13"/>
+      <c r="D9" s="12"/>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A10" s="22" t="s">
+      <c r="A10" s="21" t="s">
         <v>171</v>
       </c>
-      <c r="B10" s="22" t="s">
+      <c r="B10" s="21" t="s">
         <v>252</v>
       </c>
-      <c r="C10" s="26">
+      <c r="C10" s="25">
         <v>0.8226</v>
       </c>
-      <c r="D10" s="13"/>
+      <c r="D10" s="12"/>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A11" s="13"/>
-      <c r="B11" s="13"/>
-      <c r="C11" s="13"/>
-      <c r="D11" s="13"/>
+      <c r="A11" s="12"/>
+      <c r="B11" s="12"/>
+      <c r="C11" s="12"/>
+      <c r="D11" s="12"/>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A12" s="13"/>
-      <c r="B12" s="13"/>
-      <c r="C12" s="13"/>
-      <c r="D12" s="13"/>
+      <c r="A12" s="12"/>
+      <c r="B12" s="12"/>
+      <c r="C12" s="12"/>
+      <c r="D12" s="12"/>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A13" s="13"/>
-      <c r="B13" s="13"/>
-      <c r="C13" s="13"/>
-      <c r="D13" s="13"/>
+      <c r="A13" s="12"/>
+      <c r="B13" s="12"/>
+      <c r="C13" s="12"/>
+      <c r="D13" s="12"/>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A14" s="13"/>
-      <c r="B14" s="13"/>
-      <c r="C14" s="13"/>
-      <c r="D14" s="13"/>
+      <c r="A14" s="12"/>
+      <c r="B14" s="12"/>
+      <c r="C14" s="12"/>
+      <c r="D14" s="12"/>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A15" s="13"/>
-      <c r="B15" s="13"/>
-      <c r="C15" s="13"/>
-      <c r="D15" s="13"/>
+      <c r="A15" s="12"/>
+      <c r="B15" s="12"/>
+      <c r="C15" s="12"/>
+      <c r="D15" s="12"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+  <headerFooter>
+    <oddHeader>&amp;C&amp;"Aptos"&amp;10&amp;K000000 CLASSIFICATION: CONFIDENTIAL - COMMERCIAL IN CONFIDENCE&amp;1#_x000D_</oddHeader>
+  </headerFooter>
   <tableParts count="1">
     <tablePart r:id="rId1"/>
   </tableParts>
@@ -3011,10 +3030,10 @@
   <dimension ref="A1:C13"/>
   <sheetFormatPr defaultColWidth="10.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="22.5703125" style="18" customWidth="1"/>
-    <col min="2" max="2" width="68" style="18" customWidth="1"/>
-    <col min="3" max="3" width="59.5703125" style="18" customWidth="1"/>
-    <col min="4" max="16384" width="10.85546875" style="18"/>
+    <col min="1" max="1" width="22.5703125" style="17" customWidth="1"/>
+    <col min="2" max="2" width="68" style="17" customWidth="1"/>
+    <col min="3" max="3" width="59.5703125" style="17" customWidth="1"/>
+    <col min="4" max="16384" width="10.85546875" style="17"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
@@ -3153,6 +3172,9 @@
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+  <headerFooter>
+    <oddHeader>&amp;C&amp;"Aptos"&amp;10&amp;K000000 CLASSIFICATION: CONFIDENTIAL - COMMERCIAL IN CONFIDENCE&amp;1#_x000D_</oddHeader>
+  </headerFooter>
   <tableParts count="1">
     <tablePart r:id="rId1"/>
   </tableParts>
@@ -3164,607 +3186,621 @@
   <dimension ref="A1:B8"/>
   <sheetFormatPr defaultColWidth="10.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="17.140625" style="14" customWidth="1"/>
-    <col min="2" max="2" width="107.85546875" style="14" customWidth="1"/>
-    <col min="3" max="16384" width="10.85546875" style="14"/>
+    <col min="1" max="1" width="17.140625" style="13" customWidth="1"/>
+    <col min="2" max="2" width="107.85546875" style="13" customWidth="1"/>
+    <col min="3" max="16384" width="10.85546875" style="13"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="17" t="s">
+      <c r="A1" s="16" t="s">
         <v>28</v>
       </c>
-      <c r="B1" s="19"/>
+      <c r="B1" s="18"/>
     </row>
     <row r="2" spans="1:2" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="20" t="s">
+      <c r="A2" s="19" t="s">
         <v>13</v>
       </c>
-      <c r="B2" s="19"/>
+      <c r="B2" s="18"/>
     </row>
     <row r="3" spans="1:2" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="16" t="s">
+      <c r="A3" s="15" t="s">
         <v>29</v>
       </c>
-      <c r="B3" s="16" t="s">
+      <c r="B3" s="15" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="4" spans="1:2" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="15" t="s">
+      <c r="A4" s="14" t="s">
         <v>31</v>
       </c>
-      <c r="B4" s="15" t="s">
+      <c r="B4" s="14" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="5" spans="1:2" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="15" t="s">
+      <c r="A5" s="14" t="s">
         <v>33</v>
       </c>
-      <c r="B5" s="15" t="s">
+      <c r="B5" s="14" t="s">
         <v>34</v>
       </c>
     </row>
     <row r="6" spans="1:2" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="15" t="s">
+      <c r="A6" s="14" t="s">
         <v>35</v>
       </c>
-      <c r="B6" s="15" t="s">
+      <c r="B6" s="14" t="s">
         <v>36</v>
       </c>
     </row>
     <row r="7" spans="1:2" ht="30.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="15" t="s">
+      <c r="A7" s="14" t="s">
         <v>37</v>
       </c>
-      <c r="B7" s="15" t="s">
+      <c r="B7" s="14" t="s">
         <v>38</v>
       </c>
     </row>
     <row r="8" spans="1:2" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="15" t="s">
+      <c r="A8" s="14" t="s">
         <v>39</v>
       </c>
-      <c r="B8" s="15" t="s">
+      <c r="B8" s="14" t="s">
         <v>40</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
+  <headerFooter>
+    <oddHeader>&amp;C&amp;"Aptos"&amp;10&amp;K000000 CLASSIFICATION: CONFIDENTIAL - COMMERCIAL IN CONFIDENCE&amp;1#_x000D_</oddHeader>
+  </headerFooter>
   <tableParts count="1">
-    <tablePart r:id="rId1"/>
+    <tablePart r:id="rId2"/>
   </tableParts>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="A1:E32"/>
+  <dimension ref="A1:G32"/>
   <sheetFormatPr defaultColWidth="10.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="9.5703125" style="18" customWidth="1"/>
-    <col min="2" max="2" width="21.85546875" style="14" customWidth="1"/>
-    <col min="3" max="3" width="19.85546875" style="14" customWidth="1"/>
-    <col min="4" max="4" width="24.140625" style="14" customWidth="1"/>
-    <col min="5" max="5" width="23.5703125" style="14" customWidth="1"/>
-    <col min="6" max="16384" width="10.85546875" style="14"/>
+    <col min="1" max="1" width="9.5703125" style="17" customWidth="1"/>
+    <col min="2" max="2" width="21.85546875" style="13" customWidth="1"/>
+    <col min="3" max="3" width="19.85546875" style="13" customWidth="1"/>
+    <col min="4" max="4" width="24.140625" style="13" customWidth="1"/>
+    <col min="5" max="5" width="23.5703125" style="13" customWidth="1"/>
+    <col min="6" max="16384" width="10.85546875" style="13"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="9" t="s">
+    <row r="1" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="30" t="s">
         <v>41</v>
       </c>
-      <c r="B1" s="9"/>
-    </row>
-    <row r="2" spans="1:5" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B1" s="30"/>
+      <c r="C1" s="30"/>
+      <c r="D1" s="30"/>
+      <c r="E1" s="30"/>
+      <c r="F1" s="30"/>
+      <c r="G1" s="30"/>
+    </row>
+    <row r="2" spans="1:7" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="8" t="s">
         <v>42</v>
       </c>
-      <c r="B2" s="10"/>
-    </row>
-    <row r="3" spans="1:5" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B2" s="9"/>
+    </row>
+    <row r="3" spans="1:7" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="8" t="s">
         <v>43</v>
       </c>
-      <c r="B3" s="10"/>
-    </row>
-    <row r="4" spans="1:5" ht="63.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B3" s="9"/>
+    </row>
+    <row r="4" spans="1:7" ht="63.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="B4" s="12" t="s">
+      <c r="B4" s="11" t="s">
         <v>45</v>
       </c>
-      <c r="C4" s="12" t="s">
+      <c r="C4" s="11" t="s">
         <v>46</v>
       </c>
-      <c r="D4" s="12" t="s">
+      <c r="D4" s="11" t="s">
         <v>47</v>
       </c>
-      <c r="E4" s="12" t="s">
+      <c r="E4" s="11" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A5" s="23">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A5" s="22">
         <v>1985</v>
       </c>
-      <c r="B5" s="21">
+      <c r="B5" s="20">
         <v>100</v>
       </c>
-      <c r="C5" s="21">
+      <c r="C5" s="20">
         <v>96.531589999999994</v>
       </c>
-      <c r="D5" s="21">
+      <c r="D5" s="20">
         <v>90.472560000000001</v>
       </c>
-      <c r="E5" s="21">
+      <c r="E5" s="20">
         <v>102.59062</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A6" s="23">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A6" s="22">
         <v>1986</v>
       </c>
-      <c r="B6" s="21">
+      <c r="B6" s="20">
         <v>100.6089163</v>
       </c>
-      <c r="C6" s="21">
+      <c r="C6" s="20">
         <v>97.185079999999999</v>
       </c>
-      <c r="D6" s="21">
+      <c r="D6" s="20">
         <v>92.450500000000005</v>
       </c>
-      <c r="E6" s="21">
+      <c r="E6" s="20">
         <v>101.91965999999999</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A7" s="23">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A7" s="22">
         <v>1987</v>
       </c>
-      <c r="B7" s="21">
+      <c r="B7" s="20">
         <v>96.199926230000003</v>
       </c>
-      <c r="C7" s="21">
+      <c r="C7" s="20">
         <v>97.480689999999996</v>
       </c>
-      <c r="D7" s="21">
+      <c r="D7" s="20">
         <v>93.705699999999993</v>
       </c>
-      <c r="E7" s="21">
+      <c r="E7" s="20">
         <v>101.25566999999999</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A8" s="23">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A8" s="22">
         <v>1988</v>
       </c>
-      <c r="B8" s="21">
+      <c r="B8" s="20">
         <v>88.572964889999994</v>
       </c>
-      <c r="C8" s="21">
+      <c r="C8" s="20">
         <v>97.445549999999997</v>
       </c>
-      <c r="D8" s="21">
+      <c r="D8" s="20">
         <v>94.230379999999997</v>
       </c>
-      <c r="E8" s="21">
+      <c r="E8" s="20">
         <v>100.66070999999999</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A9" s="23">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A9" s="22">
         <v>1989</v>
       </c>
-      <c r="B9" s="21">
+      <c r="B9" s="20">
         <v>98.258471139999997</v>
       </c>
-      <c r="C9" s="21">
+      <c r="C9" s="20">
         <v>97.103849999999994</v>
       </c>
-      <c r="D9" s="21">
+      <c r="D9" s="20">
         <v>94.100049999999996</v>
       </c>
-      <c r="E9" s="21">
+      <c r="E9" s="20">
         <v>100.10765000000001</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A10" s="23">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A10" s="22">
         <v>1990</v>
       </c>
-      <c r="B10" s="21">
+      <c r="B10" s="20">
         <v>94.030013929999996</v>
       </c>
-      <c r="C10" s="21">
+      <c r="C10" s="20">
         <v>96.412199999999999</v>
       </c>
-      <c r="D10" s="21">
+      <c r="D10" s="20">
         <v>93.396709999999999</v>
       </c>
-      <c r="E10" s="21">
+      <c r="E10" s="20">
         <v>99.427679999999995</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A11" s="23">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A11" s="22">
         <v>1991</v>
       </c>
-      <c r="B11" s="21">
+      <c r="B11" s="20">
         <v>91.641641320000005</v>
       </c>
-      <c r="C11" s="21">
+      <c r="C11" s="20">
         <v>95.296300000000002</v>
       </c>
-      <c r="D11" s="21">
+      <c r="D11" s="20">
         <v>92.165000000000006</v>
       </c>
-      <c r="E11" s="21">
+      <c r="E11" s="20">
         <v>98.427589999999995</v>
       </c>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A12" s="23">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A12" s="22">
         <v>1992</v>
       </c>
-      <c r="B12" s="21">
+      <c r="B12" s="20">
         <v>91.540045300000003</v>
       </c>
-      <c r="C12" s="21">
+      <c r="C12" s="20">
         <v>93.948400000000007</v>
       </c>
-      <c r="D12" s="21">
+      <c r="D12" s="20">
         <v>90.728380000000001</v>
       </c>
-      <c r="E12" s="21">
+      <c r="E12" s="20">
         <v>97.168430000000001</v>
       </c>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A13" s="23">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A13" s="22">
         <v>1993</v>
       </c>
-      <c r="B13" s="21">
+      <c r="B13" s="20">
         <v>93.210476970000002</v>
       </c>
-      <c r="C13" s="21">
+      <c r="C13" s="20">
         <v>92.431799999999996</v>
       </c>
-      <c r="D13" s="21">
+      <c r="D13" s="20">
         <v>89.139529999999993</v>
       </c>
-      <c r="E13" s="21">
+      <c r="E13" s="20">
         <v>95.724069999999998</v>
       </c>
     </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A14" s="23">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A14" s="22">
         <v>1994</v>
       </c>
-      <c r="B14" s="21">
+      <c r="B14" s="20">
         <v>95.841999670000007</v>
       </c>
-      <c r="C14" s="21">
+      <c r="C14" s="20">
         <v>90.478759999999994</v>
       </c>
-      <c r="D14" s="21">
+      <c r="D14" s="20">
         <v>87.061909999999997</v>
       </c>
-      <c r="E14" s="21">
+      <c r="E14" s="20">
         <v>93.895600000000002</v>
       </c>
     </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A15" s="23">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A15" s="22">
         <v>1995</v>
       </c>
-      <c r="B15" s="21">
+      <c r="B15" s="20">
         <v>90.321498700000006</v>
       </c>
-      <c r="C15" s="21">
+      <c r="C15" s="20">
         <v>87.821560000000005</v>
       </c>
-      <c r="D15" s="21">
+      <c r="D15" s="20">
         <v>84.321730000000002</v>
       </c>
-      <c r="E15" s="21">
+      <c r="E15" s="20">
         <v>91.321380000000005</v>
       </c>
     </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A16" s="23">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A16" s="22">
         <v>1996</v>
       </c>
-      <c r="B16" s="21">
+      <c r="B16" s="20">
         <v>84.431616199999993</v>
       </c>
-      <c r="C16" s="21">
+      <c r="C16" s="20">
         <v>83.551630000000003</v>
       </c>
-      <c r="D16" s="21">
+      <c r="D16" s="20">
         <v>80.177530000000004</v>
       </c>
-      <c r="E16" s="21">
+      <c r="E16" s="20">
         <v>86.925730000000001</v>
       </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A17" s="23">
+      <c r="A17" s="22">
         <v>1997</v>
       </c>
-      <c r="B17" s="21">
+      <c r="B17" s="20">
         <v>81.630339129999996</v>
       </c>
-      <c r="C17" s="21">
+      <c r="C17" s="20">
         <v>78.116619999999998</v>
       </c>
-      <c r="D17" s="21">
+      <c r="D17" s="20">
         <v>74.742519999999999</v>
       </c>
-      <c r="E17" s="21">
+      <c r="E17" s="20">
         <v>81.490719999999996</v>
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A18" s="23">
+      <c r="A18" s="22">
         <v>1998</v>
       </c>
-      <c r="B18" s="21">
+      <c r="B18" s="20">
         <v>73.359566150000006</v>
       </c>
-      <c r="C18" s="21">
+      <c r="C18" s="20">
         <v>73.283150000000006</v>
       </c>
-      <c r="D18" s="21">
+      <c r="D18" s="20">
         <v>69.783320000000003</v>
       </c>
-      <c r="E18" s="21">
+      <c r="E18" s="20">
         <v>76.782979999999995</v>
       </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A19" s="23">
+      <c r="A19" s="22">
         <v>1999</v>
       </c>
-      <c r="B19" s="21">
+      <c r="B19" s="20">
         <v>65.736985970000006</v>
       </c>
-      <c r="C19" s="21">
+      <c r="C19" s="20">
         <v>68.202600000000004</v>
       </c>
-      <c r="D19" s="21">
+      <c r="D19" s="20">
         <v>64.842190000000002</v>
       </c>
-      <c r="E19" s="21">
+      <c r="E19" s="20">
         <v>71.563019999999995</v>
       </c>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A20" s="23">
+      <c r="A20" s="22">
         <v>2000</v>
       </c>
-      <c r="B20" s="21">
+      <c r="B20" s="20">
         <v>62.13213185</v>
       </c>
-      <c r="C20" s="21">
+      <c r="C20" s="20">
         <v>62.079039999999999</v>
       </c>
-      <c r="D20" s="21">
+      <c r="D20" s="20">
         <v>58.843539999999997</v>
       </c>
-      <c r="E20" s="21">
+      <c r="E20" s="20">
         <v>65.314539999999994</v>
       </c>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A21" s="23">
+      <c r="A21" s="22">
         <v>2001</v>
       </c>
-      <c r="B21" s="21">
+      <c r="B21" s="20">
         <v>57.431234879999998</v>
       </c>
-      <c r="C21" s="21">
+      <c r="C21" s="20">
         <v>56.758069999999996</v>
       </c>
-      <c r="D21" s="21">
+      <c r="D21" s="20">
         <v>53.397649999999999</v>
       </c>
-      <c r="E21" s="21">
+      <c r="E21" s="20">
         <v>60.118479999999998</v>
       </c>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A22" s="23">
+      <c r="A22" s="22">
         <v>2002</v>
       </c>
-      <c r="B22" s="21">
+      <c r="B22" s="20">
         <v>52.277287010000002</v>
       </c>
-      <c r="C22" s="21">
+      <c r="C22" s="20">
         <v>54.085290000000001</v>
       </c>
-      <c r="D22" s="21">
+      <c r="D22" s="20">
         <v>50.585470000000001</v>
       </c>
-      <c r="E22" s="21">
+      <c r="E22" s="20">
         <v>57.585120000000003</v>
       </c>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A23" s="23">
+      <c r="A23" s="22">
         <v>2003</v>
       </c>
-      <c r="B23" s="21">
+      <c r="B23" s="20">
         <v>52.048872109999998</v>
       </c>
-      <c r="C23" s="21">
+      <c r="C23" s="20">
         <v>54.314309999999999</v>
       </c>
-      <c r="D23" s="21">
+      <c r="D23" s="20">
         <v>50.926110000000001</v>
       </c>
-      <c r="E23" s="21">
+      <c r="E23" s="20">
         <v>57.702509999999997</v>
       </c>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A24" s="23">
+      <c r="A24" s="22">
         <v>2004</v>
       </c>
-      <c r="B24" s="21">
+      <c r="B24" s="20">
         <v>48.32670916</v>
       </c>
-      <c r="C24" s="21">
+      <c r="C24" s="20">
         <v>56.201599999999999</v>
       </c>
-      <c r="D24" s="21">
+      <c r="D24" s="20">
         <v>52.91818</v>
       </c>
-      <c r="E24" s="21">
+      <c r="E24" s="20">
         <v>59.485010000000003</v>
       </c>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A25" s="23">
+      <c r="A25" s="22">
         <v>2005</v>
       </c>
-      <c r="B25" s="21">
+      <c r="B25" s="20">
         <v>55.745108399999999</v>
       </c>
-      <c r="C25" s="21">
+      <c r="C25" s="20">
         <v>59.347099999999998</v>
       </c>
-      <c r="D25" s="21">
+      <c r="D25" s="20">
         <v>56.115490000000001</v>
       </c>
-      <c r="E25" s="21">
+      <c r="E25" s="20">
         <v>62.578699999999998</v>
       </c>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A26" s="23">
+      <c r="A26" s="22">
         <v>2006</v>
       </c>
-      <c r="B26" s="21">
+      <c r="B26" s="20">
         <v>66.945230929999994</v>
       </c>
-      <c r="C26" s="21">
+      <c r="C26" s="20">
         <v>63.701070000000001</v>
       </c>
-      <c r="D26" s="21">
+      <c r="D26" s="20">
         <v>60.586109999999998</v>
       </c>
-      <c r="E26" s="21">
+      <c r="E26" s="20">
         <v>66.816029999999998</v>
       </c>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A27" s="23">
+      <c r="A27" s="22">
         <v>2007</v>
       </c>
-      <c r="B27" s="21">
+      <c r="B27" s="20">
         <v>70.110408460000002</v>
       </c>
-      <c r="C27" s="21">
+      <c r="C27" s="20">
         <v>69.465900000000005</v>
       </c>
-      <c r="D27" s="21">
+      <c r="D27" s="20">
         <v>66.455020000000005</v>
       </c>
-      <c r="E27" s="21">
+      <c r="E27" s="20">
         <v>72.476789999999994</v>
       </c>
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A28" s="23">
+      <c r="A28" s="22">
         <v>2008</v>
       </c>
-      <c r="B28" s="21">
+      <c r="B28" s="20">
         <v>77.378919010000004</v>
       </c>
-      <c r="C28" s="21">
+      <c r="C28" s="20">
         <v>76.619720000000001</v>
       </c>
-      <c r="D28" s="21">
+      <c r="D28" s="20">
         <v>73.616249999999994</v>
       </c>
-      <c r="E28" s="21">
+      <c r="E28" s="20">
         <v>79.623180000000005</v>
       </c>
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A29" s="23">
+      <c r="A29" s="22">
         <v>2009</v>
       </c>
-      <c r="B29" s="21">
+      <c r="B29" s="20">
         <v>95.218087100000005</v>
       </c>
-      <c r="C29" s="21">
+      <c r="C29" s="20">
         <v>85.140640000000005</v>
       </c>
-      <c r="D29" s="21">
+      <c r="D29" s="20">
         <v>81.925479999999993</v>
       </c>
-      <c r="E29" s="21">
+      <c r="E29" s="20">
         <v>88.355800000000002</v>
       </c>
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A30" s="23">
+      <c r="A30" s="22">
         <v>2010</v>
       </c>
-      <c r="B30" s="21">
+      <c r="B30" s="20">
         <v>102.2230572</v>
       </c>
-      <c r="C30" s="21">
+      <c r="C30" s="20">
         <v>95.013220000000004</v>
       </c>
-      <c r="D30" s="21">
+      <c r="D30" s="20">
         <v>91.238230000000001</v>
       </c>
-      <c r="E30" s="21">
+      <c r="E30" s="20">
         <v>98.788200000000003</v>
       </c>
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A31" s="23">
+      <c r="A31" s="22">
         <v>2011</v>
       </c>
-      <c r="B31" s="21">
+      <c r="B31" s="20">
         <v>104.49071240000001</v>
       </c>
-      <c r="C31" s="21">
+      <c r="C31" s="20">
         <v>106.24382</v>
       </c>
-      <c r="D31" s="21">
+      <c r="D31" s="20">
         <v>101.50924000000001</v>
       </c>
-      <c r="E31" s="21">
+      <c r="E31" s="20">
         <v>110.97839999999999</v>
       </c>
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A32" s="23">
+      <c r="A32" s="22">
         <v>2012</v>
       </c>
-      <c r="B32" s="21">
+      <c r="B32" s="20">
         <v>110.3549877</v>
       </c>
-      <c r="C32" s="21">
+      <c r="C32" s="20">
         <v>118.8433</v>
       </c>
-      <c r="D32" s="21">
+      <c r="D32" s="20">
         <v>112.78427000000001</v>
       </c>
-      <c r="E32" s="21">
+      <c r="E32" s="20">
         <v>124.90233000000001</v>
       </c>
     </row>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:G1"/>
+  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
+  <headerFooter>
+    <oddHeader>&amp;C&amp;"Aptos"&amp;10&amp;K000000 CLASSIFICATION: CONFIDENTIAL - COMMERCIAL IN CONFIDENCE&amp;1#_x000D_</oddHeader>
+  </headerFooter>
   <tableParts count="1">
     <tablePart r:id="rId2"/>
   </tableParts>
@@ -3773,208 +3809,224 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
-  <dimension ref="A1:E13"/>
+  <dimension ref="A1:L13"/>
   <sheetFormatPr defaultColWidth="10.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="16.7109375" style="14" customWidth="1"/>
-    <col min="2" max="2" width="13.28515625" style="14" customWidth="1"/>
-    <col min="3" max="3" width="13.140625" style="14" customWidth="1"/>
-    <col min="4" max="4" width="16.7109375" style="14" customWidth="1"/>
-    <col min="5" max="5" width="14.5703125" style="14" customWidth="1"/>
-    <col min="6" max="16384" width="10.85546875" style="14"/>
+    <col min="1" max="1" width="16.7109375" style="13" customWidth="1"/>
+    <col min="2" max="2" width="13.28515625" style="13" customWidth="1"/>
+    <col min="3" max="3" width="13.140625" style="13" customWidth="1"/>
+    <col min="4" max="4" width="16.7109375" style="13" customWidth="1"/>
+    <col min="5" max="5" width="14.5703125" style="13" customWidth="1"/>
+    <col min="6" max="16384" width="10.85546875" style="13"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="11" t="s">
+    <row r="1" spans="1:12" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="30" t="s">
         <v>49</v>
       </c>
-      <c r="B1" s="11"/>
-    </row>
-    <row r="2" spans="1:5" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="10" t="s">
+      <c r="B1" s="30"/>
+      <c r="C1" s="30"/>
+      <c r="D1" s="30"/>
+      <c r="E1" s="30"/>
+      <c r="F1" s="30"/>
+      <c r="G1" s="30"/>
+      <c r="H1" s="30"/>
+      <c r="I1" s="30"/>
+      <c r="J1" s="30"/>
+      <c r="K1" s="30"/>
+      <c r="L1" s="30"/>
+    </row>
+    <row r="2" spans="1:12" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="9" t="s">
         <v>42</v>
       </c>
-      <c r="B2" s="10"/>
-    </row>
-    <row r="3" spans="1:5" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="10" t="s">
+      <c r="B2" s="9"/>
+    </row>
+    <row r="3" spans="1:12" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="9" t="s">
         <v>43</v>
       </c>
-      <c r="B3" s="10"/>
-    </row>
-    <row r="4" spans="1:5" s="18" customFormat="1" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="12" t="s">
+      <c r="B3" s="9"/>
+    </row>
+    <row r="4" spans="1:12" s="17" customFormat="1" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="11" t="s">
         <v>50</v>
       </c>
-      <c r="B4" s="12" t="s">
+      <c r="B4" s="11" t="s">
         <v>51</v>
       </c>
-      <c r="C4" s="24" t="s">
+      <c r="C4" s="23" t="s">
         <v>52</v>
       </c>
-      <c r="D4" s="24" t="s">
+      <c r="D4" s="23" t="s">
         <v>53</v>
       </c>
-      <c r="E4" s="24" t="s">
+      <c r="E4" s="23" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="5" spans="1:5" ht="45" x14ac:dyDescent="0.25">
-      <c r="A5" s="22" t="s">
+    <row r="5" spans="1:12" ht="45" x14ac:dyDescent="0.25">
+      <c r="A5" s="21" t="s">
         <v>55</v>
       </c>
-      <c r="B5" s="22" t="s">
+      <c r="B5" s="21" t="s">
         <v>56</v>
       </c>
-      <c r="C5" s="21" t="s">
+      <c r="C5" s="20" t="s">
         <v>57</v>
       </c>
-      <c r="D5" s="25">
+      <c r="D5" s="24">
         <v>29</v>
       </c>
-      <c r="E5" s="21">
+      <c r="E5" s="20">
         <v>3.4482758620689702</v>
       </c>
     </row>
-    <row r="6" spans="1:5" ht="45" x14ac:dyDescent="0.25">
-      <c r="A6" s="22" t="s">
+    <row r="6" spans="1:12" ht="45" x14ac:dyDescent="0.25">
+      <c r="A6" s="21" t="s">
         <v>55</v>
       </c>
-      <c r="B6" s="22" t="s">
+      <c r="B6" s="21" t="s">
         <v>58</v>
       </c>
-      <c r="C6" s="21" t="s">
+      <c r="C6" s="20" t="s">
         <v>59</v>
       </c>
-      <c r="D6" s="25">
+      <c r="D6" s="24">
         <v>29</v>
       </c>
-      <c r="E6" s="21">
+      <c r="E6" s="20">
         <v>34.482758620689701</v>
       </c>
     </row>
-    <row r="7" spans="1:5" ht="45" x14ac:dyDescent="0.25">
-      <c r="A7" s="22" t="s">
+    <row r="7" spans="1:12" ht="45" x14ac:dyDescent="0.25">
+      <c r="A7" s="21" t="s">
         <v>55</v>
       </c>
-      <c r="B7" s="22" t="s">
+      <c r="B7" s="21" t="s">
         <v>60</v>
       </c>
-      <c r="C7" s="21" t="s">
+      <c r="C7" s="20" t="s">
         <v>61</v>
       </c>
-      <c r="D7" s="25">
+      <c r="D7" s="24">
         <v>29</v>
       </c>
-      <c r="E7" s="21">
+      <c r="E7" s="20">
         <v>62.068965517241402</v>
       </c>
     </row>
-    <row r="8" spans="1:5" ht="30" x14ac:dyDescent="0.25">
-      <c r="A8" s="22" t="s">
+    <row r="8" spans="1:12" ht="30" x14ac:dyDescent="0.25">
+      <c r="A8" s="21" t="s">
         <v>62</v>
       </c>
-      <c r="B8" s="22" t="s">
+      <c r="B8" s="21" t="s">
         <v>56</v>
       </c>
-      <c r="C8" s="21" t="s">
+      <c r="C8" s="20" t="s">
         <v>63</v>
       </c>
-      <c r="D8" s="25">
+      <c r="D8" s="24">
         <v>32</v>
       </c>
-      <c r="E8" s="21">
+      <c r="E8" s="20">
         <v>71.875</v>
       </c>
     </row>
-    <row r="9" spans="1:5" ht="30" x14ac:dyDescent="0.25">
-      <c r="A9" s="22" t="s">
+    <row r="9" spans="1:12" ht="30" x14ac:dyDescent="0.25">
+      <c r="A9" s="21" t="s">
         <v>62</v>
       </c>
-      <c r="B9" s="22" t="s">
+      <c r="B9" s="21" t="s">
         <v>58</v>
       </c>
-      <c r="C9" s="21" t="s">
+      <c r="C9" s="20" t="s">
         <v>64</v>
       </c>
-      <c r="D9" s="25">
+      <c r="D9" s="24">
         <v>32</v>
       </c>
-      <c r="E9" s="21">
+      <c r="E9" s="20">
         <v>9.375</v>
       </c>
     </row>
-    <row r="10" spans="1:5" ht="30" x14ac:dyDescent="0.25">
-      <c r="A10" s="22" t="s">
+    <row r="10" spans="1:12" ht="30" x14ac:dyDescent="0.25">
+      <c r="A10" s="21" t="s">
         <v>62</v>
       </c>
-      <c r="B10" s="22" t="s">
+      <c r="B10" s="21" t="s">
         <v>60</v>
       </c>
-      <c r="C10" s="21" t="s">
+      <c r="C10" s="20" t="s">
         <v>65</v>
       </c>
-      <c r="D10" s="25">
+      <c r="D10" s="24">
         <v>32</v>
       </c>
-      <c r="E10" s="21">
+      <c r="E10" s="20">
         <v>18.75</v>
       </c>
     </row>
-    <row r="11" spans="1:5" ht="30" x14ac:dyDescent="0.25">
-      <c r="A11" s="22" t="s">
+    <row r="11" spans="1:12" ht="30" x14ac:dyDescent="0.25">
+      <c r="A11" s="21" t="s">
         <v>66</v>
       </c>
-      <c r="B11" s="22" t="s">
+      <c r="B11" s="21" t="s">
         <v>56</v>
       </c>
-      <c r="C11" s="21" t="s">
+      <c r="C11" s="20" t="s">
         <v>67</v>
       </c>
-      <c r="D11" s="25">
+      <c r="D11" s="24">
         <v>27</v>
       </c>
-      <c r="E11" s="21">
+      <c r="E11" s="20">
         <v>33.3333333333333</v>
       </c>
     </row>
-    <row r="12" spans="1:5" ht="30" x14ac:dyDescent="0.25">
-      <c r="A12" s="22" t="s">
+    <row r="12" spans="1:12" ht="30" x14ac:dyDescent="0.25">
+      <c r="A12" s="21" t="s">
         <v>66</v>
       </c>
-      <c r="B12" s="22" t="s">
+      <c r="B12" s="21" t="s">
         <v>58</v>
       </c>
-      <c r="C12" s="21" t="s">
+      <c r="C12" s="20" t="s">
         <v>68</v>
       </c>
-      <c r="D12" s="25">
+      <c r="D12" s="24">
         <v>27</v>
       </c>
-      <c r="E12" s="21">
+      <c r="E12" s="20">
         <v>48.148148148148103</v>
       </c>
     </row>
-    <row r="13" spans="1:5" ht="30" x14ac:dyDescent="0.25">
-      <c r="A13" s="22" t="s">
+    <row r="13" spans="1:12" ht="30" x14ac:dyDescent="0.25">
+      <c r="A13" s="21" t="s">
         <v>66</v>
       </c>
-      <c r="B13" s="22" t="s">
+      <c r="B13" s="21" t="s">
         <v>60</v>
       </c>
-      <c r="C13" s="21" t="s">
+      <c r="C13" s="20" t="s">
         <v>69</v>
       </c>
-      <c r="D13" s="25">
+      <c r="D13" s="24">
         <v>27</v>
       </c>
-      <c r="E13" s="21">
+      <c r="E13" s="20">
         <v>18.518518518518501</v>
       </c>
     </row>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:L1"/>
+  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+  <headerFooter>
+    <oddHeader>&amp;C&amp;"Aptos"&amp;10&amp;K000000 CLASSIFICATION: CONFIDENTIAL - COMMERCIAL IN CONFIDENCE&amp;1#_x000D_</oddHeader>
+  </headerFooter>
   <tableParts count="1">
     <tablePart r:id="rId1"/>
   </tableParts>
@@ -3983,616 +4035,621 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
-  <dimension ref="A1:E74"/>
+  <dimension ref="A1:G74"/>
   <sheetFormatPr defaultColWidth="10.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="31.85546875" style="18" customWidth="1"/>
-    <col min="2" max="2" width="35.140625" style="18" customWidth="1"/>
-    <col min="3" max="3" width="21.42578125" style="18" customWidth="1"/>
-    <col min="4" max="4" width="19.5703125" style="18" customWidth="1"/>
-    <col min="5" max="5" width="20" style="18" customWidth="1"/>
-    <col min="6" max="16384" width="10.85546875" style="14"/>
+    <col min="1" max="1" width="31.85546875" style="17" customWidth="1"/>
+    <col min="2" max="2" width="35.140625" style="17" customWidth="1"/>
+    <col min="3" max="3" width="21.42578125" style="17" customWidth="1"/>
+    <col min="4" max="4" width="19.5703125" style="17" customWidth="1"/>
+    <col min="5" max="5" width="20" style="17" customWidth="1"/>
+    <col min="6" max="16384" width="10.85546875" style="13"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="9" t="s">
+    <row r="1" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="30" t="s">
         <v>70</v>
       </c>
-      <c r="B1" s="9"/>
-    </row>
-    <row r="2" spans="1:5" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B1" s="30"/>
+      <c r="C1" s="30"/>
+      <c r="D1" s="30"/>
+      <c r="E1" s="30"/>
+      <c r="F1" s="30"/>
+      <c r="G1" s="30"/>
+    </row>
+    <row r="2" spans="1:7" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="8" t="s">
         <v>42</v>
       </c>
       <c r="B2" s="8"/>
     </row>
-    <row r="3" spans="1:5" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:7" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="8" t="s">
         <v>43</v>
       </c>
       <c r="B3" s="8"/>
     </row>
-    <row r="4" spans="1:5" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:7" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="8" t="s">
         <v>71</v>
       </c>
       <c r="B4" s="8"/>
     </row>
-    <row r="5" spans="1:5" s="18" customFormat="1" ht="51.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="24" t="s">
+    <row r="5" spans="1:7" s="17" customFormat="1" ht="51.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="23" t="s">
         <v>72</v>
       </c>
-      <c r="B5" s="24" t="s">
+      <c r="B5" s="23" t="s">
         <v>73</v>
       </c>
-      <c r="C5" s="24" t="s">
+      <c r="C5" s="23" t="s">
         <v>74</v>
       </c>
-      <c r="D5" s="24" t="s">
+      <c r="D5" s="23" t="s">
         <v>75</v>
       </c>
-      <c r="E5" s="24" t="s">
+      <c r="E5" s="23" t="s">
         <v>76</v>
       </c>
     </row>
-    <row r="6" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="23" t="s">
+    <row r="6" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="22" t="s">
         <v>77</v>
       </c>
-      <c r="B6" s="23" t="s">
+      <c r="B6" s="22" t="s">
         <v>78</v>
       </c>
-      <c r="C6" s="23" t="s">
+      <c r="C6" s="22" t="s">
         <v>79</v>
       </c>
-      <c r="D6" s="23" t="s">
+      <c r="D6" s="22" t="s">
         <v>80</v>
       </c>
-      <c r="E6" s="23" t="s">
+      <c r="E6" s="22" t="s">
         <v>79</v>
       </c>
     </row>
-    <row r="7" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="23" t="s">
+    <row r="7" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="22" t="s">
         <v>81</v>
       </c>
-      <c r="B7" s="23" t="s">
+      <c r="B7" s="22" t="s">
         <v>82</v>
       </c>
-      <c r="C7" s="23" t="s">
+      <c r="C7" s="22" t="s">
         <v>58</v>
       </c>
-      <c r="D7" s="23" t="s">
+      <c r="D7" s="22" t="s">
         <v>80</v>
       </c>
-      <c r="E7" s="23" t="s">
+      <c r="E7" s="22" t="s">
         <v>79</v>
       </c>
     </row>
-    <row r="8" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="23" t="s">
+    <row r="8" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="22" t="s">
         <v>83</v>
       </c>
-      <c r="B8" s="23" t="s">
+      <c r="B8" s="22" t="s">
         <v>84</v>
       </c>
-      <c r="C8" s="23" t="s">
+      <c r="C8" s="22" t="s">
         <v>79</v>
       </c>
-      <c r="D8" s="23" t="s">
+      <c r="D8" s="22" t="s">
         <v>58</v>
       </c>
-      <c r="E8" s="23" t="s">
+      <c r="E8" s="22" t="s">
         <v>79</v>
       </c>
     </row>
-    <row r="9" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="23" t="s">
+    <row r="9" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="22" t="s">
         <v>85</v>
       </c>
-      <c r="B9" s="23" t="s">
+      <c r="B9" s="22" t="s">
         <v>86</v>
       </c>
-      <c r="C9" s="23" t="s">
+      <c r="C9" s="22" t="s">
         <v>79</v>
       </c>
-      <c r="D9" s="23" t="s">
+      <c r="D9" s="22" t="s">
         <v>58</v>
       </c>
-      <c r="E9" s="23" t="s">
+      <c r="E9" s="22" t="s">
         <v>79</v>
       </c>
     </row>
-    <row r="10" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="23" t="s">
+    <row r="10" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="22" t="s">
         <v>87</v>
       </c>
-      <c r="B10" s="23" t="s">
+      <c r="B10" s="22" t="s">
         <v>88</v>
       </c>
-      <c r="C10" s="23" t="s">
+      <c r="C10" s="22" t="s">
         <v>79</v>
       </c>
-      <c r="D10" s="23" t="s">
+      <c r="D10" s="22" t="s">
         <v>80</v>
       </c>
-      <c r="E10" s="23" t="s">
+      <c r="E10" s="22" t="s">
         <v>79</v>
       </c>
     </row>
-    <row r="11" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="23" t="s">
+    <row r="11" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="22" t="s">
         <v>89</v>
       </c>
-      <c r="B11" s="23" t="s">
+      <c r="B11" s="22" t="s">
         <v>90</v>
       </c>
-      <c r="C11" s="23" t="s">
+      <c r="C11" s="22" t="s">
         <v>80</v>
       </c>
-      <c r="D11" s="23" t="s">
+      <c r="D11" s="22" t="s">
         <v>80</v>
       </c>
-      <c r="E11" s="23" t="s">
+      <c r="E11" s="22" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="12" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="23" t="s">
+    <row r="12" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="22" t="s">
         <v>91</v>
       </c>
-      <c r="B12" s="23" t="s">
+      <c r="B12" s="22" t="s">
         <v>92</v>
       </c>
-      <c r="C12" s="23" t="s">
+      <c r="C12" s="22" t="s">
         <v>80</v>
       </c>
-      <c r="D12" s="23" t="s">
+      <c r="D12" s="22" t="s">
         <v>58</v>
       </c>
-      <c r="E12" s="23" t="s">
+      <c r="E12" s="22" t="s">
         <v>80</v>
       </c>
     </row>
-    <row r="13" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="23" t="s">
+    <row r="13" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="22" t="s">
         <v>93</v>
       </c>
-      <c r="B13" s="23" t="s">
+      <c r="B13" s="22" t="s">
         <v>94</v>
       </c>
-      <c r="C13" s="23" t="s">
+      <c r="C13" s="22" t="s">
         <v>95</v>
       </c>
-      <c r="D13" s="23" t="s">
+      <c r="D13" s="22" t="s">
         <v>95</v>
       </c>
-      <c r="E13" s="23" t="s">
+      <c r="E13" s="22" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="14" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="23" t="s">
+    <row r="14" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="22" t="s">
         <v>96</v>
       </c>
-      <c r="B14" s="23" t="s">
+      <c r="B14" s="22" t="s">
         <v>97</v>
       </c>
-      <c r="C14" s="23" t="s">
+      <c r="C14" s="22" t="s">
         <v>80</v>
       </c>
-      <c r="D14" s="23" t="s">
+      <c r="D14" s="22" t="s">
         <v>80</v>
       </c>
-      <c r="E14" s="23" t="s">
+      <c r="E14" s="22" t="s">
         <v>79</v>
       </c>
     </row>
-    <row r="15" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="23" t="s">
+    <row r="15" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="22" t="s">
         <v>98</v>
       </c>
-      <c r="B15" s="23" t="s">
+      <c r="B15" s="22" t="s">
         <v>99</v>
       </c>
-      <c r="C15" s="23" t="s">
+      <c r="C15" s="22" t="s">
         <v>95</v>
       </c>
-      <c r="D15" s="23" t="s">
+      <c r="D15" s="22" t="s">
         <v>95</v>
       </c>
-      <c r="E15" s="23" t="s">
+      <c r="E15" s="22" t="s">
         <v>80</v>
       </c>
     </row>
-    <row r="16" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="23" t="s">
+    <row r="16" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="22" t="s">
         <v>100</v>
       </c>
-      <c r="B16" s="23" t="s">
+      <c r="B16" s="22" t="s">
         <v>101</v>
       </c>
-      <c r="C16" s="23" t="s">
+      <c r="C16" s="22" t="s">
         <v>80</v>
       </c>
-      <c r="D16" s="23" t="s">
+      <c r="D16" s="22" t="s">
         <v>58</v>
       </c>
-      <c r="E16" s="23" t="s">
+      <c r="E16" s="22" t="s">
         <v>79</v>
       </c>
     </row>
     <row r="17" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="23" t="s">
+      <c r="A17" s="22" t="s">
         <v>102</v>
       </c>
-      <c r="B17" s="23" t="s">
+      <c r="B17" s="22" t="s">
         <v>103</v>
       </c>
-      <c r="C17" s="23" t="s">
+      <c r="C17" s="22" t="s">
         <v>79</v>
       </c>
-      <c r="D17" s="23" t="s">
+      <c r="D17" s="22" t="s">
         <v>80</v>
       </c>
-      <c r="E17" s="23" t="s">
+      <c r="E17" s="22" t="s">
         <v>79</v>
       </c>
     </row>
     <row r="18" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="23" t="s">
+      <c r="A18" s="22" t="s">
         <v>104</v>
       </c>
-      <c r="B18" s="23" t="s">
+      <c r="B18" s="22" t="s">
         <v>105</v>
       </c>
-      <c r="C18" s="23" t="s">
+      <c r="C18" s="22" t="s">
         <v>58</v>
       </c>
-      <c r="D18" s="23" t="s">
+      <c r="D18" s="22" t="s">
         <v>58</v>
       </c>
-      <c r="E18" s="23" t="s">
+      <c r="E18" s="22" t="s">
         <v>80</v>
       </c>
     </row>
     <row r="19" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="23" t="s">
+      <c r="A19" s="22" t="s">
         <v>106</v>
       </c>
-      <c r="B19" s="23" t="s">
+      <c r="B19" s="22" t="s">
         <v>107</v>
       </c>
-      <c r="C19" s="23" t="s">
+      <c r="C19" s="22" t="s">
         <v>80</v>
       </c>
-      <c r="D19" s="23" t="s">
+      <c r="D19" s="22" t="s">
         <v>80</v>
       </c>
-      <c r="E19" s="23" t="s">
+      <c r="E19" s="22" t="s">
         <v>80</v>
       </c>
     </row>
     <row r="20" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="23" t="s">
+      <c r="A20" s="22" t="s">
         <v>108</v>
       </c>
-      <c r="B20" s="23" t="s">
+      <c r="B20" s="22" t="s">
         <v>109</v>
       </c>
-      <c r="C20" s="23" t="s">
+      <c r="C20" s="22" t="s">
         <v>79</v>
       </c>
-      <c r="D20" s="23" t="s">
+      <c r="D20" s="22" t="s">
         <v>80</v>
       </c>
-      <c r="E20" s="23" t="s">
+      <c r="E20" s="22" t="s">
         <v>79</v>
       </c>
     </row>
     <row r="21" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="23" t="s">
+      <c r="A21" s="22" t="s">
         <v>110</v>
       </c>
-      <c r="B21" s="23" t="s">
+      <c r="B21" s="22" t="s">
         <v>111</v>
       </c>
-      <c r="C21" s="23" t="s">
+      <c r="C21" s="22" t="s">
         <v>79</v>
       </c>
-      <c r="D21" s="23" t="s">
+      <c r="D21" s="22" t="s">
         <v>80</v>
       </c>
-      <c r="E21" s="23" t="s">
+      <c r="E21" s="22" t="s">
         <v>79</v>
       </c>
     </row>
     <row r="22" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="23" t="s">
+      <c r="A22" s="22" t="s">
         <v>112</v>
       </c>
-      <c r="B22" s="23" t="s">
+      <c r="B22" s="22" t="s">
         <v>113</v>
       </c>
-      <c r="C22" s="23" t="s">
+      <c r="C22" s="22" t="s">
         <v>58</v>
       </c>
-      <c r="D22" s="23" t="s">
+      <c r="D22" s="22" t="s">
         <v>80</v>
       </c>
-      <c r="E22" s="23" t="s">
+      <c r="E22" s="22" t="s">
         <v>79</v>
       </c>
     </row>
     <row r="23" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="23" t="s">
+      <c r="A23" s="22" t="s">
         <v>114</v>
       </c>
-      <c r="B23" s="23" t="s">
+      <c r="B23" s="22" t="s">
         <v>115</v>
       </c>
-      <c r="C23" s="23" t="s">
+      <c r="C23" s="22" t="s">
         <v>80</v>
       </c>
-      <c r="D23" s="23" t="s">
+      <c r="D23" s="22" t="s">
         <v>80</v>
       </c>
-      <c r="E23" s="23" t="s">
+      <c r="E23" s="22" t="s">
         <v>79</v>
       </c>
     </row>
     <row r="24" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="23" t="s">
+      <c r="A24" s="22" t="s">
         <v>116</v>
       </c>
-      <c r="B24" s="23" t="s">
+      <c r="B24" s="22" t="s">
         <v>117</v>
       </c>
-      <c r="C24" s="23" t="s">
+      <c r="C24" s="22" t="s">
         <v>95</v>
       </c>
-      <c r="D24" s="23" t="s">
+      <c r="D24" s="22" t="s">
         <v>80</v>
       </c>
-      <c r="E24" s="23" t="s">
+      <c r="E24" s="22" t="s">
         <v>79</v>
       </c>
     </row>
     <row r="25" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="23" t="s">
+      <c r="A25" s="22" t="s">
         <v>118</v>
       </c>
-      <c r="B25" s="23" t="s">
+      <c r="B25" s="22" t="s">
         <v>119</v>
       </c>
-      <c r="C25" s="23" t="s">
+      <c r="C25" s="22" t="s">
         <v>79</v>
       </c>
-      <c r="D25" s="23" t="s">
+      <c r="D25" s="22" t="s">
         <v>80</v>
       </c>
-      <c r="E25" s="23" t="s">
+      <c r="E25" s="22" t="s">
         <v>79</v>
       </c>
     </row>
     <row r="26" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="23" t="s">
+      <c r="A26" s="22" t="s">
         <v>120</v>
       </c>
-      <c r="B26" s="23" t="s">
+      <c r="B26" s="22" t="s">
         <v>121</v>
       </c>
-      <c r="C26" s="23" t="s">
+      <c r="C26" s="22" t="s">
         <v>95</v>
       </c>
-      <c r="D26" s="23" t="s">
+      <c r="D26" s="22" t="s">
         <v>95</v>
       </c>
-      <c r="E26" s="23" t="s">
+      <c r="E26" s="22" t="s">
         <v>95</v>
       </c>
     </row>
     <row r="27" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="23" t="s">
+      <c r="A27" s="22" t="s">
         <v>122</v>
       </c>
-      <c r="B27" s="23" t="s">
+      <c r="B27" s="22" t="s">
         <v>123</v>
       </c>
-      <c r="C27" s="23" t="s">
+      <c r="C27" s="22" t="s">
         <v>58</v>
       </c>
-      <c r="D27" s="23" t="s">
+      <c r="D27" s="22" t="s">
         <v>58</v>
       </c>
-      <c r="E27" s="23" t="s">
+      <c r="E27" s="22" t="s">
         <v>58</v>
       </c>
     </row>
     <row r="28" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="23" t="s">
+      <c r="A28" s="22" t="s">
         <v>124</v>
       </c>
-      <c r="B28" s="23" t="s">
+      <c r="B28" s="22" t="s">
         <v>125</v>
       </c>
-      <c r="C28" s="23" t="s">
+      <c r="C28" s="22" t="s">
         <v>79</v>
       </c>
-      <c r="D28" s="23" t="s">
+      <c r="D28" s="22" t="s">
         <v>58</v>
       </c>
-      <c r="E28" s="23" t="s">
+      <c r="E28" s="22" t="s">
         <v>79</v>
       </c>
     </row>
     <row r="29" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="23" t="s">
+      <c r="A29" s="22" t="s">
         <v>126</v>
       </c>
-      <c r="B29" s="23" t="s">
+      <c r="B29" s="22" t="s">
         <v>127</v>
       </c>
-      <c r="C29" s="23" t="s">
+      <c r="C29" s="22" t="s">
         <v>79</v>
       </c>
-      <c r="D29" s="23" t="s">
+      <c r="D29" s="22" t="s">
         <v>58</v>
       </c>
-      <c r="E29" s="23" t="s">
+      <c r="E29" s="22" t="s">
         <v>79</v>
       </c>
     </row>
     <row r="30" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="23" t="s">
+      <c r="A30" s="22" t="s">
         <v>128</v>
       </c>
-      <c r="B30" s="23" t="s">
+      <c r="B30" s="22" t="s">
         <v>129</v>
       </c>
-      <c r="C30" s="23" t="s">
+      <c r="C30" s="22" t="s">
         <v>80</v>
       </c>
-      <c r="D30" s="23" t="s">
+      <c r="D30" s="22" t="s">
         <v>80</v>
       </c>
-      <c r="E30" s="23" t="s">
+      <c r="E30" s="22" t="s">
         <v>58</v>
       </c>
     </row>
     <row r="31" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="23" t="s">
+      <c r="A31" s="22" t="s">
         <v>130</v>
       </c>
-      <c r="B31" s="23" t="s">
+      <c r="B31" s="22" t="s">
         <v>131</v>
       </c>
-      <c r="C31" s="23" t="s">
+      <c r="C31" s="22" t="s">
         <v>58</v>
       </c>
-      <c r="D31" s="23" t="s">
+      <c r="D31" s="22" t="s">
         <v>58</v>
       </c>
-      <c r="E31" s="23" t="s">
+      <c r="E31" s="22" t="s">
         <v>58</v>
       </c>
     </row>
     <row r="32" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="23" t="s">
+      <c r="A32" s="22" t="s">
         <v>132</v>
       </c>
-      <c r="B32" s="23" t="s">
+      <c r="B32" s="22" t="s">
         <v>133</v>
       </c>
-      <c r="C32" s="23" t="s">
+      <c r="C32" s="22" t="s">
         <v>95</v>
       </c>
-      <c r="D32" s="23" t="s">
+      <c r="D32" s="22" t="s">
         <v>95</v>
       </c>
-      <c r="E32" s="23" t="s">
+      <c r="E32" s="22" t="s">
         <v>58</v>
       </c>
     </row>
     <row r="33" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="23" t="s">
+      <c r="A33" s="22" t="s">
         <v>134</v>
       </c>
-      <c r="B33" s="23" t="s">
+      <c r="B33" s="22" t="s">
         <v>135</v>
       </c>
-      <c r="C33" s="23" t="s">
+      <c r="C33" s="22" t="s">
         <v>80</v>
       </c>
-      <c r="D33" s="23" t="s">
+      <c r="D33" s="22" t="s">
         <v>80</v>
       </c>
-      <c r="E33" s="23" t="s">
+      <c r="E33" s="22" t="s">
         <v>79</v>
       </c>
     </row>
     <row r="34" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A34" s="23" t="s">
+      <c r="A34" s="22" t="s">
         <v>136</v>
       </c>
-      <c r="B34" s="23" t="s">
+      <c r="B34" s="22" t="s">
         <v>137</v>
       </c>
-      <c r="C34" s="23" t="s">
+      <c r="C34" s="22" t="s">
         <v>80</v>
       </c>
-      <c r="D34" s="23" t="s">
+      <c r="D34" s="22" t="s">
         <v>80</v>
       </c>
-      <c r="E34" s="23" t="s">
+      <c r="E34" s="22" t="s">
         <v>79</v>
       </c>
     </row>
     <row r="35" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A35" s="23" t="s">
+      <c r="A35" s="22" t="s">
         <v>138</v>
       </c>
-      <c r="B35" s="23" t="s">
+      <c r="B35" s="22" t="s">
         <v>139</v>
       </c>
-      <c r="C35" s="23" t="s">
+      <c r="C35" s="22" t="s">
         <v>79</v>
       </c>
-      <c r="D35" s="23" t="s">
+      <c r="D35" s="22" t="s">
         <v>80</v>
       </c>
-      <c r="E35" s="23" t="s">
+      <c r="E35" s="22" t="s">
         <v>79</v>
       </c>
     </row>
     <row r="36" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A36" s="23" t="s">
+      <c r="A36" s="22" t="s">
         <v>140</v>
       </c>
-      <c r="B36" s="23" t="s">
+      <c r="B36" s="22" t="s">
         <v>141</v>
       </c>
-      <c r="C36" s="23" t="s">
+      <c r="C36" s="22" t="s">
         <v>79</v>
       </c>
-      <c r="D36" s="23" t="s">
+      <c r="D36" s="22" t="s">
         <v>80</v>
       </c>
-      <c r="E36" s="23" t="s">
+      <c r="E36" s="22" t="s">
         <v>79</v>
       </c>
     </row>
     <row r="37" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A37" s="23" t="s">
+      <c r="A37" s="22" t="s">
         <v>142</v>
       </c>
-      <c r="B37" s="23" t="s">
+      <c r="B37" s="22" t="s">
         <v>143</v>
       </c>
-      <c r="C37" s="23" t="s">
+      <c r="C37" s="22" t="s">
         <v>95</v>
       </c>
-      <c r="D37" s="23" t="s">
+      <c r="D37" s="22" t="s">
         <v>80</v>
       </c>
-      <c r="E37" s="23" t="s">
+      <c r="E37" s="22" t="s">
         <v>79</v>
       </c>
     </row>
     <row r="38" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A38" s="23" t="s">
+      <c r="A38" s="22" t="s">
         <v>144</v>
       </c>
-      <c r="B38" s="23" t="s">
+      <c r="B38" s="22" t="s">
         <v>145</v>
       </c>
-      <c r="C38" s="23" t="s">
+      <c r="C38" s="22" t="s">
         <v>79</v>
       </c>
-      <c r="D38" s="23" t="s">
+      <c r="D38" s="22" t="s">
         <v>58</v>
       </c>
-      <c r="E38" s="23" t="s">
+      <c r="E38" s="22" t="s">
         <v>79</v>
       </c>
     </row>
@@ -4633,8 +4690,14 @@
     <row r="73" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="74" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:G1"/>
+  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+  <headerFooter>
+    <oddHeader>&amp;C&amp;"Aptos"&amp;10&amp;K000000 CLASSIFICATION: CONFIDENTIAL - COMMERCIAL IN CONFIDENCE&amp;1#_x000D_</oddHeader>
+  </headerFooter>
   <tableParts count="1">
     <tablePart r:id="rId1"/>
   </tableParts>
@@ -4643,531 +4706,537 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
-  <dimension ref="A1:E74"/>
+  <dimension ref="A1:H74"/>
   <sheetFormatPr defaultColWidth="10.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="8.85546875" style="14" customWidth="1"/>
-    <col min="2" max="2" width="15.140625" style="14" customWidth="1"/>
-    <col min="3" max="3" width="15.5703125" style="14" customWidth="1"/>
-    <col min="4" max="4" width="24.85546875" style="14" customWidth="1"/>
-    <col min="5" max="5" width="24.42578125" style="14" customWidth="1"/>
-    <col min="6" max="16384" width="10.85546875" style="14"/>
+    <col min="1" max="1" width="8.85546875" style="13" customWidth="1"/>
+    <col min="2" max="2" width="15.140625" style="13" customWidth="1"/>
+    <col min="3" max="3" width="15.5703125" style="13" customWidth="1"/>
+    <col min="4" max="4" width="24.85546875" style="13" customWidth="1"/>
+    <col min="5" max="5" width="24.42578125" style="13" customWidth="1"/>
+    <col min="6" max="16384" width="10.85546875" style="13"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="11" t="s">
+    <row r="1" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="30" t="s">
         <v>146</v>
       </c>
-      <c r="B1" s="9"/>
-    </row>
-    <row r="2" spans="1:5" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="10" t="s">
+      <c r="B1" s="30"/>
+      <c r="C1" s="30"/>
+      <c r="D1" s="30"/>
+      <c r="E1" s="30"/>
+      <c r="F1" s="30"/>
+      <c r="G1" s="30"/>
+      <c r="H1" s="30"/>
+    </row>
+    <row r="2" spans="1:8" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="9" t="s">
         <v>147</v>
       </c>
-      <c r="B2" s="10"/>
-    </row>
-    <row r="3" spans="1:5" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="10" t="s">
+      <c r="B2" s="9"/>
+    </row>
+    <row r="3" spans="1:8" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="9" t="s">
         <v>43</v>
       </c>
-      <c r="B3" s="10"/>
-    </row>
-    <row r="4" spans="1:5" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="10" t="s">
+      <c r="B3" s="9"/>
+    </row>
+    <row r="4" spans="1:8" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="9" t="s">
         <v>71</v>
       </c>
-      <c r="B4" s="10"/>
-    </row>
-    <row r="5" spans="1:5" ht="63" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="16" t="s">
+      <c r="B4" s="9"/>
+    </row>
+    <row r="5" spans="1:8" ht="63" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="15" t="s">
         <v>44</v>
       </c>
-      <c r="B5" s="12" t="s">
+      <c r="B5" s="11" t="s">
         <v>148</v>
       </c>
-      <c r="C5" s="12" t="s">
+      <c r="C5" s="11" t="s">
         <v>46</v>
       </c>
-      <c r="D5" s="12" t="s">
+      <c r="D5" s="11" t="s">
         <v>47</v>
       </c>
-      <c r="E5" s="12" t="s">
+      <c r="E5" s="11" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="6" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="22" t="s">
+    <row r="6" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="21" t="s">
         <v>149</v>
       </c>
-      <c r="B6" s="21">
+      <c r="B6" s="20">
         <v>100</v>
       </c>
-      <c r="C6" s="21">
+      <c r="C6" s="20">
         <v>98.756069213325404</v>
       </c>
-      <c r="D6" s="21">
+      <c r="D6" s="20">
         <v>92.349339719694399</v>
       </c>
-      <c r="E6" s="21">
+      <c r="E6" s="20">
         <v>105.162798706956</v>
       </c>
     </row>
-    <row r="7" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="22" t="s">
+    <row r="7" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="21" t="s">
         <v>150</v>
       </c>
-      <c r="B7" s="21">
+      <c r="B7" s="20">
         <v>97.854051774469895</v>
       </c>
-      <c r="C7" s="21">
+      <c r="C7" s="20">
         <v>102.21349113510701</v>
       </c>
-      <c r="D7" s="21">
+      <c r="D7" s="20">
         <v>98.2852770814564</v>
       </c>
-      <c r="E7" s="21">
+      <c r="E7" s="20">
         <v>106.141705188758</v>
       </c>
     </row>
-    <row r="8" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="22" t="s">
+    <row r="8" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="21" t="s">
         <v>151</v>
       </c>
-      <c r="B8" s="21">
+      <c r="B8" s="20">
         <v>108.839612640252</v>
       </c>
-      <c r="C8" s="21">
+      <c r="C8" s="20">
         <v>104.59035878180801</v>
       </c>
-      <c r="D8" s="21">
+      <c r="D8" s="20">
         <v>100.800527438472</v>
       </c>
-      <c r="E8" s="21">
+      <c r="E8" s="20">
         <v>108.380190125144</v>
       </c>
     </row>
-    <row r="9" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="22" t="s">
+    <row r="9" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="21" t="s">
         <v>152</v>
       </c>
-      <c r="B9" s="21">
+      <c r="B9" s="20">
         <v>108.039366053359</v>
       </c>
-      <c r="C9" s="21">
+      <c r="C9" s="20">
         <v>106.166128471211</v>
       </c>
-      <c r="D9" s="21">
+      <c r="D9" s="20">
         <v>102.100236335343</v>
       </c>
-      <c r="E9" s="21">
+      <c r="E9" s="20">
         <v>110.232020607077</v>
       </c>
     </row>
-    <row r="10" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="22" t="s">
+    <row r="10" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="21" t="s">
         <v>153</v>
       </c>
-      <c r="B10" s="21">
+      <c r="B10" s="20">
         <v>102.02483066637301</v>
       </c>
-      <c r="C10" s="21">
+      <c r="C10" s="20">
         <v>106.444913799663</v>
       </c>
-      <c r="D10" s="21">
+      <c r="D10" s="20">
         <v>102.05384511996</v>
       </c>
-      <c r="E10" s="21">
+      <c r="E10" s="20">
         <v>110.835982479368</v>
       </c>
     </row>
-    <row r="11" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="22" t="s">
+    <row r="11" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="21" t="s">
         <v>154</v>
       </c>
-      <c r="B11" s="21">
+      <c r="B11" s="20">
         <v>107.84253966043801</v>
       </c>
-      <c r="C11" s="21">
+      <c r="C11" s="20">
         <v>105.330228291716</v>
       </c>
-      <c r="D11" s="21">
+      <c r="D11" s="20">
         <v>100.939159612013</v>
       </c>
-      <c r="E11" s="21">
+      <c r="E11" s="20">
         <v>109.72129697142</v>
       </c>
     </row>
-    <row r="12" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="22" t="s">
+    <row r="12" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="21" t="s">
         <v>155</v>
       </c>
-      <c r="B12" s="21">
+      <c r="B12" s="20">
         <v>106.787881441172</v>
       </c>
-      <c r="C12" s="21">
+      <c r="C12" s="20">
         <v>105.727214053412</v>
       </c>
-      <c r="D12" s="21">
+      <c r="D12" s="20">
         <v>101.336145373709</v>
       </c>
-      <c r="E12" s="21">
+      <c r="E12" s="20">
         <v>110.118282733117</v>
       </c>
     </row>
-    <row r="13" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="22" t="s">
+    <row r="13" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="21" t="s">
         <v>156</v>
       </c>
-      <c r="B13" s="21">
+      <c r="B13" s="20">
         <v>103.36432197068601</v>
       </c>
-      <c r="C13" s="21">
+      <c r="C13" s="20">
         <v>106.948707416837</v>
       </c>
-      <c r="D13" s="21">
+      <c r="D13" s="20">
         <v>102.557638737134</v>
       </c>
-      <c r="E13" s="21">
+      <c r="E13" s="20">
         <v>111.339776096541</v>
       </c>
     </row>
-    <row r="14" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="22" t="s">
+    <row r="14" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="21" t="s">
         <v>157</v>
       </c>
-      <c r="B14" s="21">
+      <c r="B14" s="20">
         <v>109.908166619472</v>
       </c>
-      <c r="C14" s="21">
+      <c r="C14" s="20">
         <v>107.78389296019201</v>
       </c>
-      <c r="D14" s="21">
+      <c r="D14" s="20">
         <v>103.718000824325</v>
       </c>
-      <c r="E14" s="21">
+      <c r="E14" s="20">
         <v>111.849785096058</v>
       </c>
     </row>
-    <row r="15" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="22" t="s">
+    <row r="15" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="21" t="s">
         <v>158</v>
       </c>
-      <c r="B15" s="21">
+      <c r="B15" s="20">
         <v>109.731994326492</v>
       </c>
-      <c r="C15" s="21">
+      <c r="C15" s="20">
         <v>107.691464324181</v>
       </c>
-      <c r="D15" s="21">
+      <c r="D15" s="20">
         <v>103.901632980844</v>
       </c>
-      <c r="E15" s="21">
+      <c r="E15" s="20">
         <v>111.481295667515</v>
       </c>
     </row>
-    <row r="16" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="22" t="s">
+    <row r="16" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="21" t="s">
         <v>159</v>
       </c>
-      <c r="B16" s="21">
+      <c r="B16" s="20">
         <v>105.727425566002</v>
       </c>
-      <c r="C16" s="21">
+      <c r="C16" s="20">
         <v>106.98078694739201</v>
       </c>
-      <c r="D16" s="21">
+      <c r="D16" s="20">
         <v>103.052572893741</v>
       </c>
-      <c r="E16" s="21">
+      <c r="E16" s="20">
         <v>110.909001001042</v>
       </c>
     </row>
     <row r="17" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="22" t="s">
+      <c r="A17" s="21" t="s">
         <v>160</v>
       </c>
-      <c r="B17" s="21">
+      <c r="B17" s="20">
         <v>105.481857138642</v>
       </c>
-      <c r="C17" s="21">
+      <c r="C17" s="20">
         <v>105.465383756864</v>
       </c>
-      <c r="D17" s="21">
+      <c r="D17" s="20">
         <v>99.056777847878905</v>
       </c>
-      <c r="E17" s="21">
+      <c r="E17" s="20">
         <v>111.873989665848</v>
       </c>
     </row>
     <row r="18" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="22" t="s">
+      <c r="A18" s="21" t="s">
         <v>161</v>
       </c>
-      <c r="B18" s="21" t="s">
+      <c r="B18" s="20" t="s">
         <v>95</v>
       </c>
-      <c r="C18" s="21" t="s">
+      <c r="C18" s="20" t="s">
         <v>95</v>
       </c>
-      <c r="D18" s="21" t="s">
+      <c r="D18" s="20" t="s">
         <v>95</v>
       </c>
-      <c r="E18" s="21" t="s">
+      <c r="E18" s="20" t="s">
         <v>95</v>
       </c>
     </row>
     <row r="19" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="22" t="s">
+      <c r="A19" s="21" t="s">
         <v>162</v>
       </c>
-      <c r="B19" s="21" t="s">
+      <c r="B19" s="20" t="s">
         <v>95</v>
       </c>
-      <c r="C19" s="21" t="s">
+      <c r="C19" s="20" t="s">
         <v>95</v>
       </c>
-      <c r="D19" s="21" t="s">
+      <c r="D19" s="20" t="s">
         <v>95</v>
       </c>
-      <c r="E19" s="21" t="s">
+      <c r="E19" s="20" t="s">
         <v>95</v>
       </c>
     </row>
     <row r="20" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="22" t="s">
+      <c r="A20" s="21" t="s">
         <v>163</v>
       </c>
-      <c r="B20" s="21">
+      <c r="B20" s="20">
         <v>100</v>
       </c>
-      <c r="C20" s="21">
+      <c r="C20" s="20">
         <v>104.503099346775</v>
       </c>
-      <c r="D20" s="21">
+      <c r="D20" s="20">
         <v>92.080486661890603</v>
       </c>
-      <c r="E20" s="21">
+      <c r="E20" s="20">
         <v>116.925712031659</v>
       </c>
     </row>
     <row r="21" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="22" t="s">
+      <c r="A21" s="21" t="s">
         <v>164</v>
       </c>
-      <c r="B21" s="21">
+      <c r="B21" s="20">
         <v>96.334508898973695</v>
       </c>
-      <c r="C21" s="21">
+      <c r="C21" s="20">
         <v>94.176782235660895</v>
       </c>
-      <c r="D21" s="21">
+      <c r="D21" s="20">
         <v>86.396809624855507</v>
       </c>
-      <c r="E21" s="21">
+      <c r="E21" s="20">
         <v>101.956754846466</v>
       </c>
     </row>
     <row r="22" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="22" t="s">
+      <c r="A22" s="21" t="s">
         <v>165</v>
       </c>
-      <c r="B22" s="21">
+      <c r="B22" s="20">
         <v>93.354284014682605</v>
       </c>
-      <c r="C22" s="21">
+      <c r="C22" s="20">
         <v>83.268452342385203</v>
       </c>
-      <c r="D22" s="21">
+      <c r="D22" s="20">
         <v>76.296396621587206</v>
       </c>
-      <c r="E22" s="21">
+      <c r="E22" s="20">
         <v>90.2405080631831</v>
       </c>
     </row>
     <row r="23" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="22" t="s">
+      <c r="A23" s="21" t="s">
         <v>166</v>
       </c>
-      <c r="B23" s="21">
+      <c r="B23" s="20">
         <v>71.015956424037896</v>
       </c>
-      <c r="C23" s="21">
+      <c r="C23" s="20">
         <v>72.701509393257794</v>
       </c>
-      <c r="D23" s="21">
+      <c r="D23" s="20">
         <v>65.155750408316393</v>
       </c>
-      <c r="E23" s="21">
+      <c r="E23" s="20">
         <v>80.247268378199195</v>
       </c>
     </row>
     <row r="24" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="22" t="s">
+      <c r="A24" s="21" t="s">
         <v>167</v>
       </c>
-      <c r="B24" s="21">
+      <c r="B24" s="20">
         <v>63.7820812006049</v>
       </c>
-      <c r="C24" s="21">
+      <c r="C24" s="20">
         <v>61.4004536905884</v>
       </c>
-      <c r="D24" s="21">
+      <c r="D24" s="20">
         <v>53.985774311096201</v>
       </c>
-      <c r="E24" s="21">
+      <c r="E24" s="20">
         <v>68.815133070080606</v>
       </c>
     </row>
     <row r="25" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="22" t="s">
+      <c r="A25" s="21" t="s">
         <v>168</v>
       </c>
-      <c r="B25" s="21">
+      <c r="B25" s="20">
         <v>47.8583509019603</v>
       </c>
-      <c r="C25" s="21">
+      <c r="C25" s="20">
         <v>51.862654930090699</v>
       </c>
-      <c r="D25" s="21">
+      <c r="D25" s="20">
         <v>44.029485031248903</v>
       </c>
-      <c r="E25" s="21">
+      <c r="E25" s="20">
         <v>59.6958248289328</v>
       </c>
     </row>
     <row r="26" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="22" t="s">
+      <c r="A26" s="21" t="s">
         <v>169</v>
       </c>
-      <c r="B26" s="21">
+      <c r="B26" s="20">
         <v>43.586671965715702</v>
       </c>
-      <c r="C26" s="21">
+      <c r="C26" s="20">
         <v>47.652063937048403</v>
       </c>
-      <c r="D26" s="21">
+      <c r="D26" s="20">
         <v>39.818894038206501</v>
       </c>
-      <c r="E26" s="21">
+      <c r="E26" s="20">
         <v>55.485233835890298</v>
       </c>
     </row>
     <row r="27" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="22" t="s">
+      <c r="A27" s="21" t="s">
         <v>170</v>
       </c>
-      <c r="B27" s="21">
+      <c r="B27" s="20">
         <v>52.8472832420495</v>
       </c>
-      <c r="C27" s="21">
+      <c r="C27" s="20">
         <v>47.010661914705899</v>
       </c>
-      <c r="D27" s="21">
+      <c r="D27" s="20">
         <v>39.764666591993603</v>
       </c>
-      <c r="E27" s="21">
+      <c r="E27" s="20">
         <v>54.256657237418302</v>
       </c>
     </row>
     <row r="28" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="22" t="s">
+      <c r="A28" s="21" t="s">
         <v>171</v>
       </c>
-      <c r="B28" s="21">
+      <c r="B28" s="20">
         <v>51.735195784359199</v>
       </c>
-      <c r="C28" s="21">
+      <c r="C28" s="20">
         <v>49.624210879368597</v>
       </c>
-      <c r="D28" s="21">
+      <c r="D28" s="20">
         <v>41.791040980526702</v>
       </c>
-      <c r="E28" s="21">
+      <c r="E28" s="20">
         <v>57.457380778210599</v>
       </c>
     </row>
     <row r="29" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="22" t="s">
+      <c r="A29" s="21" t="s">
         <v>172</v>
       </c>
-      <c r="B29" s="21">
+      <c r="B29" s="20">
         <v>46.231511626754703</v>
       </c>
-      <c r="C29" s="21">
+      <c r="C29" s="20">
         <v>55.586417551161297</v>
       </c>
-      <c r="D29" s="21">
+      <c r="D29" s="20">
         <v>48.171738171668999</v>
       </c>
-      <c r="E29" s="21">
+      <c r="E29" s="20">
         <v>63.001096930653603</v>
       </c>
     </row>
     <row r="30" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="22" t="s">
+      <c r="A30" s="21" t="s">
         <v>173</v>
       </c>
-      <c r="B30" s="21">
+      <c r="B30" s="20">
         <v>63.896266317985997</v>
       </c>
-      <c r="C30" s="21">
+      <c r="C30" s="20">
         <v>61.697392077532299</v>
       </c>
-      <c r="D30" s="21">
+      <c r="D30" s="20">
         <v>54.151633092590899</v>
       </c>
-      <c r="E30" s="21">
+      <c r="E30" s="20">
         <v>69.2431510624738</v>
       </c>
     </row>
     <row r="31" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="22" t="s">
+      <c r="A31" s="21" t="s">
         <v>174</v>
       </c>
-      <c r="B31" s="21">
+      <c r="B31" s="20">
         <v>78.292987366662402</v>
       </c>
-      <c r="C31" s="21">
+      <c r="C31" s="20">
         <v>65.271235276711806</v>
       </c>
-      <c r="D31" s="21">
+      <c r="D31" s="20">
         <v>58.299179555913902</v>
       </c>
-      <c r="E31" s="21">
+      <c r="E31" s="20">
         <v>72.243290997509803</v>
       </c>
     </row>
     <row r="32" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="22" t="s">
+      <c r="A32" s="21" t="s">
         <v>175</v>
       </c>
-      <c r="B32" s="21">
+      <c r="B32" s="20">
         <v>65.572521214769495</v>
       </c>
-      <c r="C32" s="21">
+      <c r="C32" s="20">
         <v>67.879887510627</v>
       </c>
-      <c r="D32" s="21">
+      <c r="D32" s="20">
         <v>60.099914899821499</v>
       </c>
-      <c r="E32" s="21">
+      <c r="E32" s="20">
         <v>75.659860121432402</v>
       </c>
     </row>
     <row r="33" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="22" t="s">
+      <c r="A33" s="21" t="s">
         <v>176</v>
       </c>
-      <c r="B33" s="21">
+      <c r="B33" s="20">
         <v>66.006931498474501</v>
       </c>
-      <c r="C33" s="21">
+      <c r="C33" s="20">
         <v>68.854504481017102</v>
       </c>
-      <c r="D33" s="21">
+      <c r="D33" s="20">
         <v>56.431891796133002</v>
       </c>
-      <c r="E33" s="21">
+      <c r="E33" s="20">
         <v>81.277117165901203</v>
       </c>
     </row>
@@ -5213,8 +5282,14 @@
     <row r="73" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="74" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:H1"/>
+  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+  <headerFooter>
+    <oddHeader>&amp;C&amp;"Aptos"&amp;10&amp;K000000 CLASSIFICATION: CONFIDENTIAL - COMMERCIAL IN CONFIDENCE&amp;1#_x000D_</oddHeader>
+  </headerFooter>
   <ignoredErrors>
     <ignoredError sqref="A6:A33" numberStoredAsText="1"/>
   </ignoredErrors>
@@ -5229,148 +5304,148 @@
   <dimension ref="A1:E73"/>
   <sheetFormatPr defaultColWidth="10.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="18.85546875" style="14" customWidth="1"/>
-    <col min="2" max="2" width="12.85546875" style="14" customWidth="1"/>
-    <col min="3" max="3" width="10.42578125" style="14" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="14" customWidth="1"/>
-    <col min="5" max="5" width="13" style="14" customWidth="1"/>
-    <col min="6" max="16384" width="10.85546875" style="14"/>
+    <col min="1" max="1" width="18.85546875" style="13" customWidth="1"/>
+    <col min="2" max="2" width="12.85546875" style="13" customWidth="1"/>
+    <col min="3" max="3" width="10.42578125" style="13" customWidth="1"/>
+    <col min="4" max="4" width="14.85546875" style="13" customWidth="1"/>
+    <col min="5" max="5" width="13" style="13" customWidth="1"/>
+    <col min="6" max="16384" width="10.85546875" style="13"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="11" t="s">
+      <c r="A1" s="10" t="s">
         <v>177</v>
       </c>
-      <c r="B1" s="11"/>
+      <c r="B1" s="10"/>
     </row>
     <row r="2" spans="1:5" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="10" t="s">
+      <c r="A2" s="9" t="s">
         <v>147</v>
       </c>
-      <c r="B2" s="10"/>
+      <c r="B2" s="9"/>
     </row>
     <row r="3" spans="1:5" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="10" t="s">
+      <c r="A3" s="9" t="s">
         <v>43</v>
       </c>
-      <c r="B3" s="10"/>
-    </row>
-    <row r="4" spans="1:5" s="18" customFormat="1" ht="66.599999999999994" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="24" t="s">
+      <c r="B3" s="9"/>
+    </row>
+    <row r="4" spans="1:5" s="17" customFormat="1" ht="66.599999999999994" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="23" t="s">
         <v>50</v>
       </c>
-      <c r="B4" s="24" t="s">
+      <c r="B4" s="23" t="s">
         <v>51</v>
       </c>
-      <c r="C4" s="24" t="s">
+      <c r="C4" s="23" t="s">
         <v>52</v>
       </c>
-      <c r="D4" s="24" t="s">
+      <c r="D4" s="23" t="s">
         <v>53</v>
       </c>
-      <c r="E4" s="24" t="s">
+      <c r="E4" s="23" t="s">
         <v>54</v>
       </c>
     </row>
     <row r="5" spans="1:5" ht="30" x14ac:dyDescent="0.25">
-      <c r="A5" s="22" t="s">
+      <c r="A5" s="21" t="s">
         <v>178</v>
       </c>
-      <c r="B5" s="22" t="s">
+      <c r="B5" s="21" t="s">
         <v>56</v>
       </c>
-      <c r="C5" s="21" t="s">
+      <c r="C5" s="20" t="s">
         <v>179</v>
       </c>
-      <c r="D5" s="25">
+      <c r="D5" s="24">
         <v>25</v>
       </c>
-      <c r="E5" s="21">
+      <c r="E5" s="20">
         <v>16</v>
       </c>
     </row>
     <row r="6" spans="1:5" ht="30" x14ac:dyDescent="0.25">
-      <c r="A6" s="22" t="s">
+      <c r="A6" s="21" t="s">
         <v>178</v>
       </c>
-      <c r="B6" s="22" t="s">
+      <c r="B6" s="21" t="s">
         <v>58</v>
       </c>
-      <c r="C6" s="21" t="s">
+      <c r="C6" s="20" t="s">
         <v>180</v>
       </c>
-      <c r="D6" s="25">
+      <c r="D6" s="24">
         <v>25</v>
       </c>
-      <c r="E6" s="21">
+      <c r="E6" s="20">
         <v>76</v>
       </c>
     </row>
     <row r="7" spans="1:5" ht="30" x14ac:dyDescent="0.25">
-      <c r="A7" s="22" t="s">
+      <c r="A7" s="21" t="s">
         <v>178</v>
       </c>
-      <c r="B7" s="22" t="s">
+      <c r="B7" s="21" t="s">
         <v>60</v>
       </c>
-      <c r="C7" s="21" t="s">
+      <c r="C7" s="20" t="s">
         <v>181</v>
       </c>
-      <c r="D7" s="25">
+      <c r="D7" s="24">
         <v>25</v>
       </c>
-      <c r="E7" s="21">
+      <c r="E7" s="20">
         <v>8</v>
       </c>
     </row>
     <row r="8" spans="1:5" ht="30" x14ac:dyDescent="0.25">
-      <c r="A8" s="22" t="s">
+      <c r="A8" s="21" t="s">
         <v>182</v>
       </c>
-      <c r="B8" s="22" t="s">
+      <c r="B8" s="21" t="s">
         <v>56</v>
       </c>
-      <c r="C8" s="21" t="s">
+      <c r="C8" s="20" t="s">
         <v>179</v>
       </c>
-      <c r="D8" s="25">
+      <c r="D8" s="24">
         <v>23</v>
       </c>
-      <c r="E8" s="21">
+      <c r="E8" s="20">
         <v>17.3913043478261</v>
       </c>
     </row>
     <row r="9" spans="1:5" ht="30" x14ac:dyDescent="0.25">
-      <c r="A9" s="22" t="s">
+      <c r="A9" s="21" t="s">
         <v>182</v>
       </c>
-      <c r="B9" s="22" t="s">
+      <c r="B9" s="21" t="s">
         <v>58</v>
       </c>
-      <c r="C9" s="21" t="s">
+      <c r="C9" s="20" t="s">
         <v>65</v>
       </c>
-      <c r="D9" s="25">
+      <c r="D9" s="24">
         <v>23</v>
       </c>
-      <c r="E9" s="21">
+      <c r="E9" s="20">
         <v>26.086956521739101</v>
       </c>
     </row>
     <row r="10" spans="1:5" ht="30" x14ac:dyDescent="0.25">
-      <c r="A10" s="22" t="s">
+      <c r="A10" s="21" t="s">
         <v>182</v>
       </c>
-      <c r="B10" s="22" t="s">
+      <c r="B10" s="21" t="s">
         <v>60</v>
       </c>
-      <c r="C10" s="21" t="s">
+      <c r="C10" s="20" t="s">
         <v>68</v>
       </c>
-      <c r="D10" s="25">
+      <c r="D10" s="24">
         <v>23</v>
       </c>
-      <c r="E10" s="21">
+      <c r="E10" s="20">
         <v>56.521739130434803</v>
       </c>
     </row>
@@ -5435,6 +5510,9 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+  <headerFooter>
+    <oddHeader>&amp;C&amp;"Aptos"&amp;10&amp;K000000 CLASSIFICATION: CONFIDENTIAL - COMMERCIAL IN CONFIDENCE&amp;1#_x000D_</oddHeader>
+  </headerFooter>
   <tableParts count="1">
     <tablePart r:id="rId1"/>
   </tableParts>
@@ -5446,474 +5524,477 @@
   <dimension ref="A1:D35"/>
   <sheetFormatPr defaultColWidth="10.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="28.5703125" style="14" customWidth="1"/>
-    <col min="2" max="2" width="27.5703125" style="14" customWidth="1"/>
-    <col min="3" max="3" width="20.85546875" style="14" customWidth="1"/>
-    <col min="4" max="4" width="18.85546875" style="14" customWidth="1"/>
-    <col min="5" max="16384" width="10.85546875" style="14"/>
+    <col min="1" max="1" width="28.5703125" style="13" customWidth="1"/>
+    <col min="2" max="2" width="27.5703125" style="13" customWidth="1"/>
+    <col min="3" max="3" width="20.85546875" style="13" customWidth="1"/>
+    <col min="4" max="4" width="18.85546875" style="13" customWidth="1"/>
+    <col min="5" max="16384" width="10.85546875" style="13"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="11" t="s">
+      <c r="A1" s="10" t="s">
         <v>183</v>
       </c>
-      <c r="B1" s="11"/>
+      <c r="B1" s="10"/>
     </row>
     <row r="2" spans="1:4" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="10" t="s">
+      <c r="A2" s="9" t="s">
         <v>147</v>
       </c>
-      <c r="B2" s="10"/>
+      <c r="B2" s="9"/>
     </row>
     <row r="3" spans="1:4" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="10" t="s">
+      <c r="A3" s="9" t="s">
         <v>43</v>
       </c>
-      <c r="B3" s="10"/>
+      <c r="B3" s="9"/>
     </row>
     <row r="4" spans="1:4" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="10" t="s">
+      <c r="A4" s="9" t="s">
         <v>71</v>
       </c>
-      <c r="B4" s="10"/>
+      <c r="B4" s="9"/>
     </row>
     <row r="5" spans="1:4" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="12" t="s">
+      <c r="A5" s="11" t="s">
         <v>72</v>
       </c>
-      <c r="B5" s="12" t="s">
+      <c r="B5" s="11" t="s">
         <v>73</v>
       </c>
-      <c r="C5" s="12" t="s">
+      <c r="C5" s="11" t="s">
         <v>184</v>
       </c>
-      <c r="D5" s="12" t="s">
+      <c r="D5" s="11" t="s">
         <v>185</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A6" s="22" t="s">
+      <c r="A6" s="21" t="s">
         <v>186</v>
       </c>
-      <c r="B6" s="22" t="s">
+      <c r="B6" s="21" t="s">
         <v>187</v>
       </c>
-      <c r="C6" s="22" t="s">
+      <c r="C6" s="21" t="s">
         <v>58</v>
       </c>
-      <c r="D6" s="22" t="s">
+      <c r="D6" s="21" t="s">
         <v>58</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A7" s="22" t="s">
+      <c r="A7" s="21" t="s">
         <v>188</v>
       </c>
-      <c r="B7" s="22" t="s">
+      <c r="B7" s="21" t="s">
         <v>189</v>
       </c>
-      <c r="C7" s="22" t="s">
+      <c r="C7" s="21" t="s">
         <v>58</v>
       </c>
-      <c r="D7" s="22" t="s">
+      <c r="D7" s="21" t="s">
         <v>79</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A8" s="22" t="s">
+      <c r="A8" s="21" t="s">
         <v>190</v>
       </c>
-      <c r="B8" s="22" t="s">
+      <c r="B8" s="21" t="s">
         <v>191</v>
       </c>
-      <c r="C8" s="22" t="s">
+      <c r="C8" s="21" t="s">
         <v>58</v>
       </c>
-      <c r="D8" s="22" t="s">
+      <c r="D8" s="21" t="s">
         <v>80</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A9" s="22" t="s">
+      <c r="A9" s="21" t="s">
         <v>192</v>
       </c>
-      <c r="B9" s="22" t="s">
+      <c r="B9" s="21" t="s">
         <v>193</v>
       </c>
-      <c r="C9" s="22" t="s">
+      <c r="C9" s="21" t="s">
         <v>79</v>
       </c>
-      <c r="D9" s="22" t="s">
+      <c r="D9" s="21" t="s">
         <v>79</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A10" s="22" t="s">
+      <c r="A10" s="21" t="s">
         <v>194</v>
       </c>
-      <c r="B10" s="22" t="s">
+      <c r="B10" s="21" t="s">
         <v>195</v>
       </c>
-      <c r="C10" s="22" t="s">
+      <c r="C10" s="21" t="s">
         <v>58</v>
       </c>
-      <c r="D10" s="22" t="s">
+      <c r="D10" s="21" t="s">
         <v>79</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A11" s="22" t="s">
+      <c r="A11" s="21" t="s">
         <v>196</v>
       </c>
-      <c r="B11" s="22" t="s">
+      <c r="B11" s="21" t="s">
         <v>197</v>
       </c>
-      <c r="C11" s="22" t="s">
+      <c r="C11" s="21" t="s">
         <v>79</v>
       </c>
-      <c r="D11" s="22" t="s">
+      <c r="D11" s="21" t="s">
         <v>80</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A12" s="22" t="s">
+      <c r="A12" s="21" t="s">
         <v>198</v>
       </c>
-      <c r="B12" s="22" t="s">
+      <c r="B12" s="21" t="s">
         <v>199</v>
       </c>
-      <c r="C12" s="22" t="s">
+      <c r="C12" s="21" t="s">
         <v>80</v>
       </c>
-      <c r="D12" s="22" t="s">
+      <c r="D12" s="21" t="s">
         <v>80</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A13" s="22" t="s">
+      <c r="A13" s="21" t="s">
         <v>200</v>
       </c>
-      <c r="B13" s="22" t="s">
+      <c r="B13" s="21" t="s">
         <v>201</v>
       </c>
-      <c r="C13" s="22" t="s">
+      <c r="C13" s="21" t="s">
         <v>58</v>
       </c>
-      <c r="D13" s="22" t="s">
+      <c r="D13" s="21" t="s">
         <v>58</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A14" s="22" t="s">
+      <c r="A14" s="21" t="s">
         <v>202</v>
       </c>
-      <c r="B14" s="22" t="s">
+      <c r="B14" s="21" t="s">
         <v>203</v>
       </c>
-      <c r="C14" s="22" t="s">
+      <c r="C14" s="21" t="s">
         <v>58</v>
       </c>
-      <c r="D14" s="22" t="s">
+      <c r="D14" s="21" t="s">
         <v>80</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A15" s="22" t="s">
+      <c r="A15" s="21" t="s">
         <v>204</v>
       </c>
-      <c r="B15" s="22" t="s">
+      <c r="B15" s="21" t="s">
         <v>205</v>
       </c>
-      <c r="C15" s="22" t="s">
+      <c r="C15" s="21" t="s">
         <v>58</v>
       </c>
-      <c r="D15" s="22" t="s">
+      <c r="D15" s="21" t="s">
         <v>79</v>
       </c>
     </row>
     <row r="16" spans="1:4" ht="30" x14ac:dyDescent="0.25">
-      <c r="A16" s="22" t="s">
+      <c r="A16" s="21" t="s">
         <v>206</v>
       </c>
-      <c r="B16" s="22" t="s">
+      <c r="B16" s="21" t="s">
         <v>207</v>
       </c>
-      <c r="C16" s="22" t="s">
+      <c r="C16" s="21" t="s">
         <v>58</v>
       </c>
-      <c r="D16" s="22" t="s">
+      <c r="D16" s="21" t="s">
         <v>80</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A17" s="22" t="s">
+      <c r="A17" s="21" t="s">
         <v>208</v>
       </c>
-      <c r="B17" s="22" t="s">
+      <c r="B17" s="21" t="s">
         <v>209</v>
       </c>
-      <c r="C17" s="22" t="s">
+      <c r="C17" s="21" t="s">
         <v>58</v>
       </c>
-      <c r="D17" s="22" t="s">
+      <c r="D17" s="21" t="s">
         <v>58</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A18" s="22" t="s">
+      <c r="A18" s="21" t="s">
         <v>210</v>
       </c>
-      <c r="B18" s="22" t="s">
+      <c r="B18" s="21" t="s">
         <v>211</v>
       </c>
-      <c r="C18" s="22" t="s">
+      <c r="C18" s="21" t="s">
         <v>58</v>
       </c>
-      <c r="D18" s="22" t="s">
+      <c r="D18" s="21" t="s">
         <v>80</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A19" s="22" t="s">
+      <c r="A19" s="21" t="s">
         <v>212</v>
       </c>
-      <c r="B19" s="22" t="s">
+      <c r="B19" s="21" t="s">
         <v>213</v>
       </c>
-      <c r="C19" s="22" t="s">
+      <c r="C19" s="21" t="s">
         <v>79</v>
       </c>
-      <c r="D19" s="22" t="s">
+      <c r="D19" s="21" t="s">
         <v>80</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A20" s="22" t="s">
+      <c r="A20" s="21" t="s">
         <v>214</v>
       </c>
-      <c r="B20" s="22" t="s">
+      <c r="B20" s="21" t="s">
         <v>215</v>
       </c>
-      <c r="C20" s="22" t="s">
+      <c r="C20" s="21" t="s">
         <v>95</v>
       </c>
-      <c r="D20" s="22" t="s">
+      <c r="D20" s="21" t="s">
         <v>58</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A21" s="22" t="s">
+      <c r="A21" s="21" t="s">
         <v>216</v>
       </c>
-      <c r="B21" s="22" t="s">
+      <c r="B21" s="21" t="s">
         <v>217</v>
       </c>
-      <c r="C21" s="22" t="s">
+      <c r="C21" s="21" t="s">
         <v>58</v>
       </c>
-      <c r="D21" s="22" t="s">
+      <c r="D21" s="21" t="s">
         <v>95</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A22" s="22" t="s">
+      <c r="A22" s="21" t="s">
         <v>218</v>
       </c>
-      <c r="B22" s="22" t="s">
+      <c r="B22" s="21" t="s">
         <v>219</v>
       </c>
-      <c r="C22" s="22" t="s">
+      <c r="C22" s="21" t="s">
         <v>58</v>
       </c>
-      <c r="D22" s="22" t="s">
+      <c r="D22" s="21" t="s">
         <v>80</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A23" s="22" t="s">
+      <c r="A23" s="21" t="s">
         <v>220</v>
       </c>
-      <c r="B23" s="22" t="s">
+      <c r="B23" s="21" t="s">
         <v>221</v>
       </c>
-      <c r="C23" s="22" t="s">
+      <c r="C23" s="21" t="s">
         <v>58</v>
       </c>
-      <c r="D23" s="22" t="s">
+      <c r="D23" s="21" t="s">
         <v>95</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A24" s="22" t="s">
+      <c r="A24" s="21" t="s">
         <v>222</v>
       </c>
-      <c r="B24" s="22" t="s">
+      <c r="B24" s="21" t="s">
         <v>223</v>
       </c>
-      <c r="C24" s="22" t="s">
+      <c r="C24" s="21" t="s">
         <v>58</v>
       </c>
-      <c r="D24" s="22" t="s">
+      <c r="D24" s="21" t="s">
         <v>80</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A25" s="22" t="s">
+      <c r="A25" s="21" t="s">
         <v>224</v>
       </c>
-      <c r="B25" s="22" t="s">
+      <c r="B25" s="21" t="s">
         <v>225</v>
       </c>
-      <c r="C25" s="22" t="s">
+      <c r="C25" s="21" t="s">
         <v>95</v>
       </c>
-      <c r="D25" s="22" t="s">
+      <c r="D25" s="21" t="s">
         <v>58</v>
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A26" s="22" t="s">
+      <c r="A26" s="21" t="s">
         <v>226</v>
       </c>
-      <c r="B26" s="22" t="s">
+      <c r="B26" s="21" t="s">
         <v>227</v>
       </c>
-      <c r="C26" s="22" t="s">
+      <c r="C26" s="21" t="s">
         <v>80</v>
       </c>
-      <c r="D26" s="22" t="s">
+      <c r="D26" s="21" t="s">
         <v>58</v>
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A27" s="22" t="s">
+      <c r="A27" s="21" t="s">
         <v>228</v>
       </c>
-      <c r="B27" s="22" t="s">
+      <c r="B27" s="21" t="s">
         <v>229</v>
       </c>
-      <c r="C27" s="22" t="s">
+      <c r="C27" s="21" t="s">
         <v>58</v>
       </c>
-      <c r="D27" s="22" t="s">
+      <c r="D27" s="21" t="s">
         <v>80</v>
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A28" s="22" t="s">
+      <c r="A28" s="21" t="s">
         <v>230</v>
       </c>
-      <c r="B28" s="22" t="s">
+      <c r="B28" s="21" t="s">
         <v>231</v>
       </c>
-      <c r="C28" s="22" t="s">
+      <c r="C28" s="21" t="s">
         <v>95</v>
       </c>
-      <c r="D28" s="22" t="s">
+      <c r="D28" s="21" t="s">
         <v>95</v>
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A29" s="22" t="s">
+      <c r="A29" s="21" t="s">
         <v>232</v>
       </c>
-      <c r="B29" s="22" t="s">
+      <c r="B29" s="21" t="s">
         <v>233</v>
       </c>
-      <c r="C29" s="22" t="s">
+      <c r="C29" s="21" t="s">
         <v>58</v>
       </c>
-      <c r="D29" s="22" t="s">
+      <c r="D29" s="21" t="s">
         <v>95</v>
       </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A30" s="22" t="s">
+      <c r="A30" s="21" t="s">
         <v>234</v>
       </c>
-      <c r="B30" s="22" t="s">
+      <c r="B30" s="21" t="s">
         <v>235</v>
       </c>
-      <c r="C30" s="22" t="s">
+      <c r="C30" s="21" t="s">
         <v>95</v>
       </c>
-      <c r="D30" s="22" t="s">
+      <c r="D30" s="21" t="s">
         <v>80</v>
       </c>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A31" s="22" t="s">
+      <c r="A31" s="21" t="s">
         <v>236</v>
       </c>
-      <c r="B31" s="22" t="s">
+      <c r="B31" s="21" t="s">
         <v>237</v>
       </c>
-      <c r="C31" s="22" t="s">
+      <c r="C31" s="21" t="s">
         <v>58</v>
       </c>
-      <c r="D31" s="22" t="s">
+      <c r="D31" s="21" t="s">
         <v>95</v>
       </c>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A32" s="22" t="s">
+      <c r="A32" s="21" t="s">
         <v>238</v>
       </c>
-      <c r="B32" s="22" t="s">
+      <c r="B32" s="21" t="s">
         <v>239</v>
       </c>
-      <c r="C32" s="22" t="s">
+      <c r="C32" s="21" t="s">
         <v>58</v>
       </c>
-      <c r="D32" s="22" t="s">
+      <c r="D32" s="21" t="s">
         <v>95</v>
       </c>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A33" s="22" t="s">
+      <c r="A33" s="21" t="s">
         <v>240</v>
       </c>
-      <c r="B33" s="22" t="s">
+      <c r="B33" s="21" t="s">
         <v>241</v>
       </c>
-      <c r="C33" s="22" t="s">
+      <c r="C33" s="21" t="s">
         <v>58</v>
       </c>
-      <c r="D33" s="22" t="s">
+      <c r="D33" s="21" t="s">
         <v>80</v>
       </c>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A34" s="22" t="s">
+      <c r="A34" s="21" t="s">
         <v>242</v>
       </c>
-      <c r="B34" s="22" t="s">
+      <c r="B34" s="21" t="s">
         <v>243</v>
       </c>
-      <c r="C34" s="22" t="s">
+      <c r="C34" s="21" t="s">
         <v>95</v>
       </c>
-      <c r="D34" s="22" t="s">
+      <c r="D34" s="21" t="s">
         <v>95</v>
       </c>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A35" s="22" t="s">
+      <c r="A35" s="21" t="s">
         <v>244</v>
       </c>
-      <c r="B35" s="22" t="s">
+      <c r="B35" s="21" t="s">
         <v>245</v>
       </c>
-      <c r="C35" s="22" t="s">
+      <c r="C35" s="21" t="s">
         <v>79</v>
       </c>
-      <c r="D35" s="22" t="s">
+      <c r="D35" s="21" t="s">
         <v>80</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+  <headerFooter>
+    <oddHeader>&amp;C&amp;"Aptos"&amp;10&amp;K000000 CLASSIFICATION: CONFIDENTIAL - COMMERCIAL IN CONFIDENCE&amp;1#_x000D_</oddHeader>
+  </headerFooter>
   <tableParts count="1">
     <tablePart r:id="rId1"/>
   </tableParts>
